--- a/Data/Soil/F013B4_SoilAnalysis_KRT.xlsx
+++ b/Data/Soil/F013B4_SoilAnalysis_KRT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\Soil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E930DE6D-94CC-4207-B38A-C0BA4EE2C00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE48086-DDE3-4717-8ADF-444DCCB1E9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16260" yWindow="-21540" windowWidth="18210" windowHeight="20895" xr2:uid="{1A173641-F086-4E78-91C4-BB4E9D448844}"/>
+    <workbookView xWindow="-1320" yWindow="-26460" windowWidth="17655" windowHeight="15615" xr2:uid="{1A173641-F086-4E78-91C4-BB4E9D448844}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDF" sheetId="1" r:id="rId1"/>
@@ -48,15 +48,6 @@
   </si>
   <si>
     <t>Depth</t>
-  </si>
-  <si>
-    <t>SLSND</t>
-  </si>
-  <si>
-    <t>SLSLT</t>
-  </si>
-  <si>
-    <t>SLCLY</t>
   </si>
   <si>
     <t>Plot</t>
@@ -788,13 +779,22 @@
     <t>2017-p04-4</t>
   </si>
   <si>
-    <t>SLSND2</t>
+    <t>SLSND_GBM</t>
   </si>
   <si>
-    <t>SLSLT2</t>
+    <t>SLSLT_GBM</t>
   </si>
   <si>
-    <t>SLCLY2</t>
+    <t>SLCLY_GBM</t>
+  </si>
+  <si>
+    <t>SLSND_GB</t>
+  </si>
+  <si>
+    <t>SLSLT_GB</t>
+  </si>
+  <si>
+    <t>SLCLY_GB</t>
   </si>
 </sst>
 </file>
@@ -1187,6 +1187,10 @@
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1197,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1206,13 +1210,13 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>247</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>248</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>249</v>
       </c>
       <c r="I1" t="s">
         <v>250</v>
@@ -1235,7 +1239,7 @@
         <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -1270,7 +1274,7 @@
         <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E3">
         <v>60</v>
@@ -1305,7 +1309,7 @@
         <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -1340,7 +1344,7 @@
         <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E5">
         <v>140</v>
@@ -1375,7 +1379,7 @@
         <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E6">
         <v>180</v>
@@ -1410,7 +1414,7 @@
         <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>20</v>
@@ -1445,7 +1449,7 @@
         <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>60</v>
@@ -1480,7 +1484,7 @@
         <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1515,7 +1519,7 @@
         <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E10">
         <v>140</v>
@@ -1550,7 +1554,7 @@
         <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E11">
         <v>180</v>
@@ -1585,7 +1589,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1620,7 +1624,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E13">
         <v>60</v>
@@ -1655,7 +1659,7 @@
         <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -1690,7 +1694,7 @@
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E15">
         <v>140</v>
@@ -1725,7 +1729,7 @@
         <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E16">
         <v>180</v>
@@ -1760,7 +1764,7 @@
         <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E17">
         <v>20</v>
@@ -1795,7 +1799,7 @@
         <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1830,7 +1834,7 @@
         <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -1865,7 +1869,7 @@
         <v>104</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E20">
         <v>140</v>
@@ -1900,7 +1904,7 @@
         <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>180</v>
@@ -1935,7 +1939,7 @@
         <v>201</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E22">
         <v>20</v>
@@ -1970,7 +1974,7 @@
         <v>201</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E23">
         <v>60</v>
@@ -2005,7 +2009,7 @@
         <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -2040,7 +2044,7 @@
         <v>201</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E25">
         <v>140</v>
@@ -2075,7 +2079,7 @@
         <v>201</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E26">
         <v>180</v>
@@ -2110,7 +2114,7 @@
         <v>202</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E27">
         <v>20</v>
@@ -2145,7 +2149,7 @@
         <v>202</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E28">
         <v>60</v>
@@ -2180,7 +2184,7 @@
         <v>202</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -2215,7 +2219,7 @@
         <v>202</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E30">
         <v>140</v>
@@ -2250,7 +2254,7 @@
         <v>202</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E31">
         <v>180</v>
@@ -2285,7 +2289,7 @@
         <v>203</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E32">
         <v>20</v>
@@ -2320,7 +2324,7 @@
         <v>203</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E33">
         <v>60</v>
@@ -2355,7 +2359,7 @@
         <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -2390,7 +2394,7 @@
         <v>203</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E35">
         <v>140</v>
@@ -2425,7 +2429,7 @@
         <v>203</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E36">
         <v>180</v>
@@ -2460,7 +2464,7 @@
         <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E37">
         <v>20</v>
@@ -2495,7 +2499,7 @@
         <v>204</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E38">
         <v>60</v>
@@ -2530,7 +2534,7 @@
         <v>204</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E39">
         <v>100</v>
@@ -2565,7 +2569,7 @@
         <v>204</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E40">
         <v>140</v>
@@ -2600,7 +2604,7 @@
         <v>204</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E41">
         <v>180</v>
@@ -2635,7 +2639,7 @@
         <v>301</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E42">
         <v>20</v>
@@ -2670,7 +2674,7 @@
         <v>301</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E43">
         <v>60</v>
@@ -2705,7 +2709,7 @@
         <v>301</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E44">
         <v>100</v>
@@ -2740,7 +2744,7 @@
         <v>301</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E45">
         <v>140</v>
@@ -2775,7 +2779,7 @@
         <v>301</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E46">
         <v>180</v>
@@ -2810,7 +2814,7 @@
         <v>302</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E47">
         <v>20</v>
@@ -2845,7 +2849,7 @@
         <v>302</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E48">
         <v>60</v>
@@ -2880,7 +2884,7 @@
         <v>302</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E49">
         <v>100</v>
@@ -2915,7 +2919,7 @@
         <v>302</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E50">
         <v>140</v>
@@ -2950,7 +2954,7 @@
         <v>302</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E51">
         <v>180</v>
@@ -2985,7 +2989,7 @@
         <v>303</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E52">
         <v>20</v>
@@ -3020,7 +3024,7 @@
         <v>303</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E53">
         <v>60</v>
@@ -3055,7 +3059,7 @@
         <v>303</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E54">
         <v>100</v>
@@ -3090,7 +3094,7 @@
         <v>303</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E55">
         <v>140</v>
@@ -3125,7 +3129,7 @@
         <v>303</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E56">
         <v>180</v>
@@ -3160,7 +3164,7 @@
         <v>304</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E57">
         <v>20</v>
@@ -3195,7 +3199,7 @@
         <v>304</v>
       </c>
       <c r="D58" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E58">
         <v>60</v>
@@ -3230,7 +3234,7 @@
         <v>304</v>
       </c>
       <c r="D59" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E59">
         <v>100</v>
@@ -3265,7 +3269,7 @@
         <v>304</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E60">
         <v>140</v>
@@ -3300,7 +3304,7 @@
         <v>304</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E61">
         <v>180</v>
@@ -3335,7 +3339,7 @@
         <v>401</v>
       </c>
       <c r="D62" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E62">
         <v>20</v>
@@ -3370,7 +3374,7 @@
         <v>401</v>
       </c>
       <c r="D63" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E63">
         <v>60</v>
@@ -3405,7 +3409,7 @@
         <v>401</v>
       </c>
       <c r="D64" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E64">
         <v>100</v>
@@ -3440,7 +3444,7 @@
         <v>401</v>
       </c>
       <c r="D65" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E65">
         <v>140</v>
@@ -3475,7 +3479,7 @@
         <v>401</v>
       </c>
       <c r="D66" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E66">
         <v>180</v>
@@ -3510,7 +3514,7 @@
         <v>402</v>
       </c>
       <c r="D67" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E67">
         <v>20</v>
@@ -3545,7 +3549,7 @@
         <v>402</v>
       </c>
       <c r="D68" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E68">
         <v>60</v>
@@ -3580,7 +3584,7 @@
         <v>402</v>
       </c>
       <c r="D69" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E69">
         <v>100</v>
@@ -3615,7 +3619,7 @@
         <v>402</v>
       </c>
       <c r="D70" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E70">
         <v>140</v>
@@ -3650,7 +3654,7 @@
         <v>402</v>
       </c>
       <c r="D71" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E71">
         <v>180</v>
@@ -3685,7 +3689,7 @@
         <v>403</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E72">
         <v>20</v>
@@ -3720,7 +3724,7 @@
         <v>403</v>
       </c>
       <c r="D73" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E73">
         <v>60</v>
@@ -3755,7 +3759,7 @@
         <v>403</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E74">
         <v>100</v>
@@ -3790,7 +3794,7 @@
         <v>403</v>
       </c>
       <c r="D75" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E75">
         <v>140</v>
@@ -3825,7 +3829,7 @@
         <v>403</v>
       </c>
       <c r="D76" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E76">
         <v>180</v>
@@ -3860,7 +3864,7 @@
         <v>404</v>
       </c>
       <c r="D77" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E77">
         <v>20</v>
@@ -3895,7 +3899,7 @@
         <v>404</v>
       </c>
       <c r="D78" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E78">
         <v>60</v>
@@ -3930,7 +3934,7 @@
         <v>404</v>
       </c>
       <c r="D79" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E79">
         <v>100</v>
@@ -3965,7 +3969,7 @@
         <v>404</v>
       </c>
       <c r="D80" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E80">
         <v>140</v>
@@ -4000,7 +4004,7 @@
         <v>404</v>
       </c>
       <c r="D81" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E81">
         <v>180</v>
@@ -4035,7 +4039,7 @@
         <v>501</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E82">
         <v>20</v>
@@ -4070,7 +4074,7 @@
         <v>501</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E83">
         <v>60</v>
@@ -4105,7 +4109,7 @@
         <v>501</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E84">
         <v>100</v>
@@ -4140,7 +4144,7 @@
         <v>501</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E85">
         <v>140</v>
@@ -4175,7 +4179,7 @@
         <v>501</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E86">
         <v>180</v>
@@ -4210,7 +4214,7 @@
         <v>502</v>
       </c>
       <c r="D87" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E87">
         <v>20</v>
@@ -4245,7 +4249,7 @@
         <v>502</v>
       </c>
       <c r="D88" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E88">
         <v>60</v>
@@ -4280,7 +4284,7 @@
         <v>502</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E89">
         <v>100</v>
@@ -4315,7 +4319,7 @@
         <v>502</v>
       </c>
       <c r="D90" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E90">
         <v>140</v>
@@ -4350,7 +4354,7 @@
         <v>502</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E91">
         <v>180</v>
@@ -4385,7 +4389,7 @@
         <v>503</v>
       </c>
       <c r="D92" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E92">
         <v>20</v>
@@ -4420,7 +4424,7 @@
         <v>503</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E93">
         <v>60</v>
@@ -4455,7 +4459,7 @@
         <v>503</v>
       </c>
       <c r="D94" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E94">
         <v>100</v>
@@ -4490,7 +4494,7 @@
         <v>503</v>
       </c>
       <c r="D95" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E95">
         <v>140</v>
@@ -4525,7 +4529,7 @@
         <v>503</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E96">
         <v>180</v>
@@ -4560,7 +4564,7 @@
         <v>504</v>
       </c>
       <c r="D97" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E97">
         <v>20</v>
@@ -4595,7 +4599,7 @@
         <v>504</v>
       </c>
       <c r="D98" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E98">
         <v>60</v>
@@ -4630,7 +4634,7 @@
         <v>504</v>
       </c>
       <c r="D99" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E99">
         <v>100</v>
@@ -4665,7 +4669,7 @@
         <v>504</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E100">
         <v>140</v>
@@ -4700,7 +4704,7 @@
         <v>504</v>
       </c>
       <c r="D101" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E101">
         <v>180</v>
@@ -4735,7 +4739,7 @@
         <v>601</v>
       </c>
       <c r="D102" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E102">
         <v>20</v>
@@ -4770,7 +4774,7 @@
         <v>601</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E103">
         <v>60</v>
@@ -4805,7 +4809,7 @@
         <v>601</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E104">
         <v>100</v>
@@ -4840,7 +4844,7 @@
         <v>601</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E105">
         <v>140</v>
@@ -4875,7 +4879,7 @@
         <v>601</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E106">
         <v>180</v>
@@ -4910,7 +4914,7 @@
         <v>602</v>
       </c>
       <c r="D107" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E107">
         <v>20</v>
@@ -4945,7 +4949,7 @@
         <v>602</v>
       </c>
       <c r="D108" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E108">
         <v>60</v>
@@ -4980,7 +4984,7 @@
         <v>602</v>
       </c>
       <c r="D109" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E109">
         <v>100</v>
@@ -5015,7 +5019,7 @@
         <v>602</v>
       </c>
       <c r="D110" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E110">
         <v>140</v>
@@ -5050,7 +5054,7 @@
         <v>602</v>
       </c>
       <c r="D111" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E111">
         <v>180</v>
@@ -5085,7 +5089,7 @@
         <v>603</v>
       </c>
       <c r="D112" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E112">
         <v>20</v>
@@ -5120,7 +5124,7 @@
         <v>603</v>
       </c>
       <c r="D113" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E113">
         <v>60</v>
@@ -5155,7 +5159,7 @@
         <v>603</v>
       </c>
       <c r="D114" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E114">
         <v>100</v>
@@ -5190,7 +5194,7 @@
         <v>603</v>
       </c>
       <c r="D115" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E115">
         <v>140</v>
@@ -5225,7 +5229,7 @@
         <v>603</v>
       </c>
       <c r="D116" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E116">
         <v>180</v>
@@ -5260,7 +5264,7 @@
         <v>604</v>
       </c>
       <c r="D117" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E117">
         <v>20</v>
@@ -5295,7 +5299,7 @@
         <v>604</v>
       </c>
       <c r="D118" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E118">
         <v>60</v>
@@ -5330,7 +5334,7 @@
         <v>604</v>
       </c>
       <c r="D119" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E119">
         <v>100</v>
@@ -5365,7 +5369,7 @@
         <v>604</v>
       </c>
       <c r="D120" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E120">
         <v>140</v>
@@ -5400,7 +5404,7 @@
         <v>604</v>
       </c>
       <c r="D121" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E121">
         <v>180</v>
@@ -5435,7 +5439,7 @@
         <v>701</v>
       </c>
       <c r="D122" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E122">
         <v>20</v>
@@ -5470,7 +5474,7 @@
         <v>701</v>
       </c>
       <c r="D123" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E123">
         <v>60</v>
@@ -5505,7 +5509,7 @@
         <v>701</v>
       </c>
       <c r="D124" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E124">
         <v>100</v>
@@ -5540,7 +5544,7 @@
         <v>701</v>
       </c>
       <c r="D125" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E125">
         <v>140</v>
@@ -5575,7 +5579,7 @@
         <v>701</v>
       </c>
       <c r="D126" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E126">
         <v>180</v>
@@ -5610,7 +5614,7 @@
         <v>702</v>
       </c>
       <c r="D127" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E127">
         <v>20</v>
@@ -5645,7 +5649,7 @@
         <v>702</v>
       </c>
       <c r="D128" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E128">
         <v>60</v>
@@ -5680,7 +5684,7 @@
         <v>702</v>
       </c>
       <c r="D129" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E129">
         <v>100</v>
@@ -5715,7 +5719,7 @@
         <v>702</v>
       </c>
       <c r="D130" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E130">
         <v>140</v>
@@ -5750,7 +5754,7 @@
         <v>702</v>
       </c>
       <c r="D131" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E131">
         <v>180</v>
@@ -5785,7 +5789,7 @@
         <v>703</v>
       </c>
       <c r="D132" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E132">
         <v>20</v>
@@ -5820,7 +5824,7 @@
         <v>703</v>
       </c>
       <c r="D133" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E133">
         <v>60</v>
@@ -5855,7 +5859,7 @@
         <v>703</v>
       </c>
       <c r="D134" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E134">
         <v>100</v>
@@ -5890,7 +5894,7 @@
         <v>703</v>
       </c>
       <c r="D135" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E135">
         <v>140</v>
@@ -5925,7 +5929,7 @@
         <v>703</v>
       </c>
       <c r="D136" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E136">
         <v>180</v>
@@ -5960,7 +5964,7 @@
         <v>704</v>
       </c>
       <c r="D137" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E137">
         <v>20</v>
@@ -5995,7 +5999,7 @@
         <v>704</v>
       </c>
       <c r="D138" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E138">
         <v>60</v>
@@ -6030,7 +6034,7 @@
         <v>704</v>
       </c>
       <c r="D139" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E139">
         <v>100</v>
@@ -6065,7 +6069,7 @@
         <v>704</v>
       </c>
       <c r="D140" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E140">
         <v>140</v>
@@ -6100,7 +6104,7 @@
         <v>704</v>
       </c>
       <c r="D141" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E141">
         <v>180</v>
@@ -6135,7 +6139,7 @@
         <v>801</v>
       </c>
       <c r="D142" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E142">
         <v>20</v>
@@ -6170,7 +6174,7 @@
         <v>801</v>
       </c>
       <c r="D143" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E143">
         <v>60</v>
@@ -6205,7 +6209,7 @@
         <v>801</v>
       </c>
       <c r="D144" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E144">
         <v>100</v>
@@ -6240,7 +6244,7 @@
         <v>801</v>
       </c>
       <c r="D145" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E145">
         <v>140</v>
@@ -6275,7 +6279,7 @@
         <v>801</v>
       </c>
       <c r="D146" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E146">
         <v>180</v>
@@ -6310,7 +6314,7 @@
         <v>802</v>
       </c>
       <c r="D147" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E147">
         <v>20</v>
@@ -6345,7 +6349,7 @@
         <v>802</v>
       </c>
       <c r="D148" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E148">
         <v>60</v>
@@ -6380,7 +6384,7 @@
         <v>802</v>
       </c>
       <c r="D149" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E149">
         <v>100</v>
@@ -6415,7 +6419,7 @@
         <v>802</v>
       </c>
       <c r="D150" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E150">
         <v>140</v>
@@ -6450,7 +6454,7 @@
         <v>802</v>
       </c>
       <c r="D151" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E151">
         <v>180</v>
@@ -6485,7 +6489,7 @@
         <v>803</v>
       </c>
       <c r="D152" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E152">
         <v>20</v>
@@ -6520,7 +6524,7 @@
         <v>803</v>
       </c>
       <c r="D153" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E153">
         <v>60</v>
@@ -6555,7 +6559,7 @@
         <v>803</v>
       </c>
       <c r="D154" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E154">
         <v>100</v>
@@ -6590,7 +6594,7 @@
         <v>803</v>
       </c>
       <c r="D155" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E155">
         <v>140</v>
@@ -6625,7 +6629,7 @@
         <v>803</v>
       </c>
       <c r="D156" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E156">
         <v>180</v>
@@ -6660,7 +6664,7 @@
         <v>804</v>
       </c>
       <c r="D157" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E157">
         <v>20</v>
@@ -6695,7 +6699,7 @@
         <v>804</v>
       </c>
       <c r="D158" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E158">
         <v>60</v>
@@ -6730,7 +6734,7 @@
         <v>804</v>
       </c>
       <c r="D159" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E159">
         <v>100</v>
@@ -6765,7 +6769,7 @@
         <v>804</v>
       </c>
       <c r="D160" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E160">
         <v>140</v>
@@ -6800,7 +6804,7 @@
         <v>804</v>
       </c>
       <c r="D161" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E161">
         <v>180</v>
@@ -6835,7 +6839,7 @@
         <v>901</v>
       </c>
       <c r="D162" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E162">
         <v>20</v>
@@ -6870,7 +6874,7 @@
         <v>901</v>
       </c>
       <c r="D163" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E163">
         <v>60</v>
@@ -6905,7 +6909,7 @@
         <v>901</v>
       </c>
       <c r="D164" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E164">
         <v>100</v>
@@ -6940,7 +6944,7 @@
         <v>901</v>
       </c>
       <c r="D165" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E165">
         <v>140</v>
@@ -6975,7 +6979,7 @@
         <v>901</v>
       </c>
       <c r="D166" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E166">
         <v>180</v>
@@ -7010,7 +7014,7 @@
         <v>902</v>
       </c>
       <c r="D167" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E167">
         <v>20</v>
@@ -7045,7 +7049,7 @@
         <v>902</v>
       </c>
       <c r="D168" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E168">
         <v>60</v>
@@ -7080,7 +7084,7 @@
         <v>902</v>
       </c>
       <c r="D169" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E169">
         <v>100</v>
@@ -7115,7 +7119,7 @@
         <v>902</v>
       </c>
       <c r="D170" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E170">
         <v>140</v>
@@ -7150,7 +7154,7 @@
         <v>902</v>
       </c>
       <c r="D171" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E171">
         <v>180</v>
@@ -7185,7 +7189,7 @@
         <v>903</v>
       </c>
       <c r="D172" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E172">
         <v>20</v>
@@ -7220,7 +7224,7 @@
         <v>903</v>
       </c>
       <c r="D173" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E173">
         <v>60</v>
@@ -7255,7 +7259,7 @@
         <v>903</v>
       </c>
       <c r="D174" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E174">
         <v>100</v>
@@ -7290,7 +7294,7 @@
         <v>903</v>
       </c>
       <c r="D175" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E175">
         <v>140</v>
@@ -7325,7 +7329,7 @@
         <v>903</v>
       </c>
       <c r="D176" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E176">
         <v>180</v>
@@ -7360,7 +7364,7 @@
         <v>904</v>
       </c>
       <c r="D177" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E177">
         <v>20</v>
@@ -7395,7 +7399,7 @@
         <v>904</v>
       </c>
       <c r="D178" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E178">
         <v>60</v>
@@ -7430,7 +7434,7 @@
         <v>904</v>
       </c>
       <c r="D179" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E179">
         <v>100</v>
@@ -7465,7 +7469,7 @@
         <v>904</v>
       </c>
       <c r="D180" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E180">
         <v>140</v>
@@ -7500,7 +7504,7 @@
         <v>904</v>
       </c>
       <c r="D181" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E181">
         <v>180</v>
@@ -7535,7 +7539,7 @@
         <v>1001</v>
       </c>
       <c r="D182" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E182">
         <v>20</v>
@@ -7570,7 +7574,7 @@
         <v>1001</v>
       </c>
       <c r="D183" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E183">
         <v>60</v>
@@ -7605,7 +7609,7 @@
         <v>1001</v>
       </c>
       <c r="D184" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E184">
         <v>100</v>
@@ -7640,7 +7644,7 @@
         <v>1001</v>
       </c>
       <c r="D185" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E185">
         <v>140</v>
@@ -7675,7 +7679,7 @@
         <v>1001</v>
       </c>
       <c r="D186" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E186">
         <v>180</v>
@@ -7710,7 +7714,7 @@
         <v>1002</v>
       </c>
       <c r="D187" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E187">
         <v>20</v>
@@ -7745,7 +7749,7 @@
         <v>1002</v>
       </c>
       <c r="D188" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E188">
         <v>60</v>
@@ -7780,7 +7784,7 @@
         <v>1002</v>
       </c>
       <c r="D189" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E189">
         <v>100</v>
@@ -7815,7 +7819,7 @@
         <v>1002</v>
       </c>
       <c r="D190" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E190">
         <v>140</v>
@@ -7850,7 +7854,7 @@
         <v>1002</v>
       </c>
       <c r="D191" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E191">
         <v>180</v>
@@ -7885,7 +7889,7 @@
         <v>1003</v>
       </c>
       <c r="D192" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E192">
         <v>20</v>
@@ -7920,7 +7924,7 @@
         <v>1003</v>
       </c>
       <c r="D193" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E193">
         <v>60</v>
@@ -7955,7 +7959,7 @@
         <v>1003</v>
       </c>
       <c r="D194" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E194">
         <v>100</v>
@@ -7990,7 +7994,7 @@
         <v>1003</v>
       </c>
       <c r="D195" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E195">
         <v>140</v>
@@ -8025,7 +8029,7 @@
         <v>1003</v>
       </c>
       <c r="D196" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E196">
         <v>180</v>
@@ -8060,7 +8064,7 @@
         <v>1004</v>
       </c>
       <c r="D197" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E197">
         <v>20</v>
@@ -8095,7 +8099,7 @@
         <v>1004</v>
       </c>
       <c r="D198" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E198">
         <v>60</v>
@@ -8130,7 +8134,7 @@
         <v>1004</v>
       </c>
       <c r="D199" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E199">
         <v>100</v>
@@ -8165,7 +8169,7 @@
         <v>1004</v>
       </c>
       <c r="D200" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E200">
         <v>140</v>
@@ -8200,7 +8204,7 @@
         <v>1004</v>
       </c>
       <c r="D201" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E201">
         <v>180</v>
@@ -8235,7 +8239,7 @@
         <v>1101</v>
       </c>
       <c r="D202" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E202">
         <v>20</v>
@@ -8270,7 +8274,7 @@
         <v>1101</v>
       </c>
       <c r="D203" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E203">
         <v>60</v>
@@ -8305,7 +8309,7 @@
         <v>1101</v>
       </c>
       <c r="D204" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E204">
         <v>100</v>
@@ -8340,7 +8344,7 @@
         <v>1101</v>
       </c>
       <c r="D205" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E205">
         <v>140</v>
@@ -8375,7 +8379,7 @@
         <v>1101</v>
       </c>
       <c r="D206" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E206">
         <v>180</v>
@@ -8410,7 +8414,7 @@
         <v>1102</v>
       </c>
       <c r="D207" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E207">
         <v>20</v>
@@ -8445,7 +8449,7 @@
         <v>1102</v>
       </c>
       <c r="D208" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E208">
         <v>60</v>
@@ -8480,7 +8484,7 @@
         <v>1102</v>
       </c>
       <c r="D209" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E209">
         <v>100</v>
@@ -8515,7 +8519,7 @@
         <v>1102</v>
       </c>
       <c r="D210" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E210">
         <v>140</v>
@@ -8550,7 +8554,7 @@
         <v>1102</v>
       </c>
       <c r="D211" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E211">
         <v>180</v>
@@ -8585,7 +8589,7 @@
         <v>1103</v>
       </c>
       <c r="D212" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E212">
         <v>20</v>
@@ -8620,7 +8624,7 @@
         <v>1103</v>
       </c>
       <c r="D213" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E213">
         <v>60</v>
@@ -8655,7 +8659,7 @@
         <v>1103</v>
       </c>
       <c r="D214" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E214">
         <v>100</v>
@@ -8690,7 +8694,7 @@
         <v>1103</v>
       </c>
       <c r="D215" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E215">
         <v>140</v>
@@ -8725,7 +8729,7 @@
         <v>1103</v>
       </c>
       <c r="D216" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E216">
         <v>180</v>
@@ -8760,7 +8764,7 @@
         <v>1104</v>
       </c>
       <c r="D217" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E217">
         <v>20</v>
@@ -8795,7 +8799,7 @@
         <v>1104</v>
       </c>
       <c r="D218" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E218">
         <v>60</v>
@@ -8830,7 +8834,7 @@
         <v>1104</v>
       </c>
       <c r="D219" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E219">
         <v>100</v>
@@ -8865,7 +8869,7 @@
         <v>1104</v>
       </c>
       <c r="D220" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E220">
         <v>140</v>
@@ -8900,7 +8904,7 @@
         <v>1104</v>
       </c>
       <c r="D221" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E221">
         <v>180</v>
@@ -8935,7 +8939,7 @@
         <v>1201</v>
       </c>
       <c r="D222" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E222">
         <v>20</v>
@@ -8970,7 +8974,7 @@
         <v>1201</v>
       </c>
       <c r="D223" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E223">
         <v>60</v>
@@ -9005,7 +9009,7 @@
         <v>1201</v>
       </c>
       <c r="D224" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E224">
         <v>100</v>
@@ -9040,7 +9044,7 @@
         <v>1201</v>
       </c>
       <c r="D225" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E225">
         <v>140</v>
@@ -9075,7 +9079,7 @@
         <v>1201</v>
       </c>
       <c r="D226" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E226">
         <v>180</v>
@@ -9110,7 +9114,7 @@
         <v>1202</v>
       </c>
       <c r="D227" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E227">
         <v>20</v>
@@ -9145,7 +9149,7 @@
         <v>1202</v>
       </c>
       <c r="D228" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E228">
         <v>60</v>
@@ -9180,7 +9184,7 @@
         <v>1202</v>
       </c>
       <c r="D229" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E229">
         <v>100</v>
@@ -9215,7 +9219,7 @@
         <v>1202</v>
       </c>
       <c r="D230" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E230">
         <v>140</v>
@@ -9250,7 +9254,7 @@
         <v>1202</v>
       </c>
       <c r="D231" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E231">
         <v>180</v>
@@ -9285,7 +9289,7 @@
         <v>1203</v>
       </c>
       <c r="D232" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E232">
         <v>20</v>
@@ -9320,7 +9324,7 @@
         <v>1203</v>
       </c>
       <c r="D233" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E233">
         <v>60</v>
@@ -9355,7 +9359,7 @@
         <v>1203</v>
       </c>
       <c r="D234" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E234">
         <v>100</v>
@@ -9390,7 +9394,7 @@
         <v>1203</v>
       </c>
       <c r="D235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E235">
         <v>140</v>
@@ -9425,7 +9429,7 @@
         <v>1203</v>
       </c>
       <c r="D236" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E236">
         <v>180</v>
@@ -9460,7 +9464,7 @@
         <v>1204</v>
       </c>
       <c r="D237" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E237">
         <v>20</v>
@@ -9495,7 +9499,7 @@
         <v>1204</v>
       </c>
       <c r="D238" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E238">
         <v>60</v>
@@ -9530,7 +9534,7 @@
         <v>1204</v>
       </c>
       <c r="D239" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E239">
         <v>100</v>
@@ -9565,7 +9569,7 @@
         <v>1204</v>
       </c>
       <c r="D240" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E240">
         <v>140</v>
@@ -9600,7 +9604,7 @@
         <v>1204</v>
       </c>
       <c r="D241" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E241">
         <v>180</v>
@@ -9635,7 +9639,7 @@
         <v>1301</v>
       </c>
       <c r="D242" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E242">
         <v>20</v>
@@ -9670,7 +9674,7 @@
         <v>1301</v>
       </c>
       <c r="D243" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E243">
         <v>60</v>
@@ -9705,7 +9709,7 @@
         <v>1301</v>
       </c>
       <c r="D244" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E244">
         <v>100</v>
@@ -9740,7 +9744,7 @@
         <v>1301</v>
       </c>
       <c r="D245" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E245">
         <v>140</v>
@@ -9775,7 +9779,7 @@
         <v>1301</v>
       </c>
       <c r="D246" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E246">
         <v>180</v>
@@ -9810,7 +9814,7 @@
         <v>1302</v>
       </c>
       <c r="D247" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E247">
         <v>20</v>
@@ -9845,7 +9849,7 @@
         <v>1302</v>
       </c>
       <c r="D248" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E248">
         <v>60</v>
@@ -9880,7 +9884,7 @@
         <v>1302</v>
       </c>
       <c r="D249" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E249">
         <v>100</v>
@@ -9915,7 +9919,7 @@
         <v>1302</v>
       </c>
       <c r="D250" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E250">
         <v>140</v>
@@ -9950,7 +9954,7 @@
         <v>1302</v>
       </c>
       <c r="D251" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E251">
         <v>180</v>
@@ -9985,7 +9989,7 @@
         <v>1303</v>
       </c>
       <c r="D252" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E252">
         <v>20</v>
@@ -10020,7 +10024,7 @@
         <v>1303</v>
       </c>
       <c r="D253" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E253">
         <v>60</v>
@@ -10055,7 +10059,7 @@
         <v>1303</v>
       </c>
       <c r="D254" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E254">
         <v>100</v>
@@ -10090,7 +10094,7 @@
         <v>1303</v>
       </c>
       <c r="D255" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E255">
         <v>140</v>
@@ -10125,7 +10129,7 @@
         <v>1303</v>
       </c>
       <c r="D256" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E256">
         <v>180</v>
@@ -10160,7 +10164,7 @@
         <v>1304</v>
       </c>
       <c r="D257" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E257">
         <v>20</v>
@@ -10195,7 +10199,7 @@
         <v>1304</v>
       </c>
       <c r="D258" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E258">
         <v>60</v>
@@ -10230,7 +10234,7 @@
         <v>1304</v>
       </c>
       <c r="D259" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E259">
         <v>100</v>
@@ -10265,7 +10269,7 @@
         <v>1304</v>
       </c>
       <c r="D260" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E260">
         <v>140</v>
@@ -10300,7 +10304,7 @@
         <v>1304</v>
       </c>
       <c r="D261" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E261">
         <v>180</v>
@@ -10335,7 +10339,7 @@
         <v>1401</v>
       </c>
       <c r="D262" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E262">
         <v>20</v>
@@ -10370,7 +10374,7 @@
         <v>1401</v>
       </c>
       <c r="D263" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E263">
         <v>60</v>
@@ -10405,7 +10409,7 @@
         <v>1401</v>
       </c>
       <c r="D264" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E264">
         <v>100</v>
@@ -10440,7 +10444,7 @@
         <v>1401</v>
       </c>
       <c r="D265" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E265">
         <v>140</v>
@@ -10475,7 +10479,7 @@
         <v>1401</v>
       </c>
       <c r="D266" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E266">
         <v>180</v>
@@ -10510,7 +10514,7 @@
         <v>1402</v>
       </c>
       <c r="D267" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E267">
         <v>20</v>
@@ -10545,7 +10549,7 @@
         <v>1402</v>
       </c>
       <c r="D268" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E268">
         <v>60</v>
@@ -10580,7 +10584,7 @@
         <v>1402</v>
       </c>
       <c r="D269" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E269">
         <v>100</v>
@@ -10615,7 +10619,7 @@
         <v>1402</v>
       </c>
       <c r="D270" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E270">
         <v>140</v>
@@ -10650,7 +10654,7 @@
         <v>1402</v>
       </c>
       <c r="D271" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E271">
         <v>180</v>
@@ -10685,7 +10689,7 @@
         <v>1403</v>
       </c>
       <c r="D272" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E272">
         <v>20</v>
@@ -10720,7 +10724,7 @@
         <v>1403</v>
       </c>
       <c r="D273" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E273">
         <v>60</v>
@@ -10755,7 +10759,7 @@
         <v>1403</v>
       </c>
       <c r="D274" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E274">
         <v>100</v>
@@ -10790,7 +10794,7 @@
         <v>1403</v>
       </c>
       <c r="D275" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E275">
         <v>140</v>
@@ -10825,7 +10829,7 @@
         <v>1403</v>
       </c>
       <c r="D276" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E276">
         <v>180</v>
@@ -10860,7 +10864,7 @@
         <v>1404</v>
       </c>
       <c r="D277" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E277">
         <v>20</v>
@@ -10895,7 +10899,7 @@
         <v>1404</v>
       </c>
       <c r="D278" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E278">
         <v>60</v>
@@ -10930,7 +10934,7 @@
         <v>1404</v>
       </c>
       <c r="D279" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E279">
         <v>100</v>
@@ -10965,7 +10969,7 @@
         <v>1404</v>
       </c>
       <c r="D280" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E280">
         <v>140</v>
@@ -11000,7 +11004,7 @@
         <v>1404</v>
       </c>
       <c r="D281" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E281">
         <v>180</v>
@@ -11035,7 +11039,7 @@
         <v>1501</v>
       </c>
       <c r="D282" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E282">
         <v>20</v>
@@ -11070,7 +11074,7 @@
         <v>1501</v>
       </c>
       <c r="D283" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E283">
         <v>60</v>
@@ -11105,7 +11109,7 @@
         <v>1501</v>
       </c>
       <c r="D284" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E284">
         <v>100</v>
@@ -11140,7 +11144,7 @@
         <v>1501</v>
       </c>
       <c r="D285" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E285">
         <v>140</v>
@@ -11175,7 +11179,7 @@
         <v>1501</v>
       </c>
       <c r="D286" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E286">
         <v>180</v>
@@ -11210,7 +11214,7 @@
         <v>1502</v>
       </c>
       <c r="D287" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E287">
         <v>20</v>
@@ -11245,7 +11249,7 @@
         <v>1502</v>
       </c>
       <c r="D288" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E288">
         <v>60</v>
@@ -11280,7 +11284,7 @@
         <v>1502</v>
       </c>
       <c r="D289" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E289">
         <v>100</v>
@@ -11315,7 +11319,7 @@
         <v>1502</v>
       </c>
       <c r="D290" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E290">
         <v>140</v>
@@ -11350,7 +11354,7 @@
         <v>1502</v>
       </c>
       <c r="D291" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E291">
         <v>180</v>
@@ -11385,7 +11389,7 @@
         <v>1503</v>
       </c>
       <c r="D292" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E292">
         <v>20</v>
@@ -11420,7 +11424,7 @@
         <v>1503</v>
       </c>
       <c r="D293" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E293">
         <v>60</v>
@@ -11455,7 +11459,7 @@
         <v>1503</v>
       </c>
       <c r="D294" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E294">
         <v>100</v>
@@ -11490,7 +11494,7 @@
         <v>1503</v>
       </c>
       <c r="D295" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E295">
         <v>140</v>
@@ -11525,7 +11529,7 @@
         <v>1503</v>
       </c>
       <c r="D296" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E296">
         <v>180</v>
@@ -11560,7 +11564,7 @@
         <v>1504</v>
       </c>
       <c r="D297" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E297">
         <v>20</v>
@@ -11595,7 +11599,7 @@
         <v>1504</v>
       </c>
       <c r="D298" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E298">
         <v>60</v>
@@ -11630,7 +11634,7 @@
         <v>1504</v>
       </c>
       <c r="D299" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E299">
         <v>100</v>
@@ -11665,7 +11669,7 @@
         <v>1504</v>
       </c>
       <c r="D300" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E300">
         <v>140</v>
@@ -11700,7 +11704,7 @@
         <v>1504</v>
       </c>
       <c r="D301" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E301">
         <v>180</v>
@@ -11735,7 +11739,7 @@
         <v>1601</v>
       </c>
       <c r="D302" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E302">
         <v>20</v>
@@ -11770,7 +11774,7 @@
         <v>1601</v>
       </c>
       <c r="D303" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E303">
         <v>60</v>
@@ -11805,7 +11809,7 @@
         <v>1601</v>
       </c>
       <c r="D304" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E304">
         <v>100</v>
@@ -11840,7 +11844,7 @@
         <v>1601</v>
       </c>
       <c r="D305" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E305">
         <v>140</v>
@@ -11875,7 +11879,7 @@
         <v>1601</v>
       </c>
       <c r="D306" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E306">
         <v>180</v>
@@ -11910,7 +11914,7 @@
         <v>1602</v>
       </c>
       <c r="D307" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E307">
         <v>20</v>
@@ -11945,7 +11949,7 @@
         <v>1602</v>
       </c>
       <c r="D308" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E308">
         <v>60</v>
@@ -11980,7 +11984,7 @@
         <v>1602</v>
       </c>
       <c r="D309" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E309">
         <v>100</v>
@@ -12015,7 +12019,7 @@
         <v>1602</v>
       </c>
       <c r="D310" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E310">
         <v>140</v>
@@ -12050,7 +12054,7 @@
         <v>1602</v>
       </c>
       <c r="D311" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E311">
         <v>180</v>
@@ -12085,7 +12089,7 @@
         <v>1603</v>
       </c>
       <c r="D312" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E312">
         <v>20</v>
@@ -12120,7 +12124,7 @@
         <v>1603</v>
       </c>
       <c r="D313" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E313">
         <v>60</v>
@@ -12155,7 +12159,7 @@
         <v>1603</v>
       </c>
       <c r="D314" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E314">
         <v>100</v>
@@ -12190,7 +12194,7 @@
         <v>1603</v>
       </c>
       <c r="D315" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E315">
         <v>140</v>
@@ -12225,7 +12229,7 @@
         <v>1603</v>
       </c>
       <c r="D316" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E316">
         <v>180</v>
@@ -12260,7 +12264,7 @@
         <v>1604</v>
       </c>
       <c r="D317" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E317">
         <v>20</v>
@@ -12295,7 +12299,7 @@
         <v>1604</v>
       </c>
       <c r="D318" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E318">
         <v>60</v>
@@ -12330,7 +12334,7 @@
         <v>1604</v>
       </c>
       <c r="D319" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E319">
         <v>100</v>
@@ -12365,7 +12369,7 @@
         <v>1604</v>
       </c>
       <c r="D320" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E320">
         <v>140</v>
@@ -12400,7 +12404,7 @@
         <v>1604</v>
       </c>
       <c r="D321" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E321">
         <v>180</v>
@@ -12435,7 +12439,7 @@
         <v>604</v>
       </c>
       <c r="D322" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E322">
         <v>20</v>
@@ -12470,7 +12474,7 @@
         <v>604</v>
       </c>
       <c r="D323" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E323">
         <v>60</v>
@@ -12505,7 +12509,7 @@
         <v>604</v>
       </c>
       <c r="D324" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E324">
         <v>100</v>
@@ -12540,7 +12544,7 @@
         <v>604</v>
       </c>
       <c r="D325" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E325">
         <v>140</v>
@@ -12575,7 +12579,7 @@
         <v>604</v>
       </c>
       <c r="D326" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E326">
         <v>180</v>
@@ -12610,7 +12614,7 @@
         <v>622</v>
       </c>
       <c r="D327" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E327">
         <v>20</v>
@@ -12645,7 +12649,7 @@
         <v>622</v>
       </c>
       <c r="D328" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E328">
         <v>60</v>
@@ -12680,7 +12684,7 @@
         <v>622</v>
       </c>
       <c r="D329" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E329">
         <v>100</v>
@@ -12715,7 +12719,7 @@
         <v>622</v>
       </c>
       <c r="D330" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E330">
         <v>140</v>
@@ -12750,7 +12754,7 @@
         <v>622</v>
       </c>
       <c r="D331" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E331">
         <v>180</v>
@@ -12785,7 +12789,7 @@
         <v>1109</v>
       </c>
       <c r="D332" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E332">
         <v>20</v>
@@ -12820,7 +12824,7 @@
         <v>1109</v>
       </c>
       <c r="D333" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E333">
         <v>60</v>
@@ -12855,7 +12859,7 @@
         <v>1109</v>
       </c>
       <c r="D334" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E334">
         <v>100</v>
@@ -12890,7 +12894,7 @@
         <v>1109</v>
       </c>
       <c r="D335" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E335">
         <v>140</v>
@@ -12925,7 +12929,7 @@
         <v>1109</v>
       </c>
       <c r="D336" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E336">
         <v>180</v>
@@ -12960,7 +12964,7 @@
         <v>1926</v>
       </c>
       <c r="D337" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E337">
         <v>20</v>
@@ -12995,7 +12999,7 @@
         <v>1926</v>
       </c>
       <c r="D338" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E338">
         <v>60</v>
@@ -13030,7 +13034,7 @@
         <v>1926</v>
       </c>
       <c r="D339" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E339">
         <v>100</v>
@@ -13065,7 +13069,7 @@
         <v>1926</v>
       </c>
       <c r="D340" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E340">
         <v>140</v>
@@ -13100,7 +13104,7 @@
         <v>1926</v>
       </c>
       <c r="D341" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E341">
         <v>180</v>
@@ -13135,7 +13139,7 @@
         <v>2006</v>
       </c>
       <c r="D342" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E342">
         <v>20</v>
@@ -13170,7 +13174,7 @@
         <v>2006</v>
       </c>
       <c r="D343" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E343">
         <v>60</v>
@@ -13205,7 +13209,7 @@
         <v>2006</v>
       </c>
       <c r="D344" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E344">
         <v>100</v>
@@ -13240,7 +13244,7 @@
         <v>2006</v>
       </c>
       <c r="D345" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E345">
         <v>140</v>
@@ -13275,7 +13279,7 @@
         <v>2006</v>
       </c>
       <c r="D346" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E346">
         <v>180</v>
@@ -13310,7 +13314,7 @@
         <v>2313</v>
       </c>
       <c r="D347" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E347">
         <v>20</v>
@@ -13345,7 +13349,7 @@
         <v>2313</v>
       </c>
       <c r="D348" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E348">
         <v>60</v>
@@ -13380,7 +13384,7 @@
         <v>2313</v>
       </c>
       <c r="D349" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E349">
         <v>100</v>
@@ -13415,7 +13419,7 @@
         <v>2313</v>
       </c>
       <c r="D350" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E350">
         <v>140</v>
@@ -13450,7 +13454,7 @@
         <v>2313</v>
       </c>
       <c r="D351" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E351">
         <v>180</v>
@@ -13485,7 +13489,7 @@
         <v>2418</v>
       </c>
       <c r="D352" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E352">
         <v>20</v>
@@ -13520,7 +13524,7 @@
         <v>2418</v>
       </c>
       <c r="D353" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E353">
         <v>60</v>
@@ -13555,7 +13559,7 @@
         <v>2418</v>
       </c>
       <c r="D354" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E354">
         <v>100</v>
@@ -13590,7 +13594,7 @@
         <v>2418</v>
       </c>
       <c r="D355" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E355">
         <v>140</v>
@@ -13625,7 +13629,7 @@
         <v>2418</v>
       </c>
       <c r="D356" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E356">
         <v>180</v>
@@ -13660,7 +13664,7 @@
         <v>3415</v>
       </c>
       <c r="D357" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E357">
         <v>20</v>
@@ -13695,7 +13699,7 @@
         <v>3415</v>
       </c>
       <c r="D358" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E358">
         <v>60</v>
@@ -13730,7 +13734,7 @@
         <v>3415</v>
       </c>
       <c r="D359" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E359">
         <v>100</v>
@@ -13765,7 +13769,7 @@
         <v>3415</v>
       </c>
       <c r="D360" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E360">
         <v>140</v>
@@ -13800,7 +13804,7 @@
         <v>3415</v>
       </c>
       <c r="D361" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E361">
         <v>180</v>
@@ -13835,7 +13839,7 @@
         <v>3808</v>
       </c>
       <c r="D362" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E362">
         <v>20</v>
@@ -13870,7 +13874,7 @@
         <v>3808</v>
       </c>
       <c r="D363" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E363">
         <v>60</v>
@@ -13905,7 +13909,7 @@
         <v>3808</v>
       </c>
       <c r="D364" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E364">
         <v>100</v>
@@ -13940,7 +13944,7 @@
         <v>3808</v>
       </c>
       <c r="D365" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E365">
         <v>140</v>
@@ -13975,7 +13979,7 @@
         <v>3808</v>
       </c>
       <c r="D366" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E366">
         <v>180</v>
@@ -14010,7 +14014,7 @@
         <v>4823</v>
       </c>
       <c r="D367" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E367">
         <v>20</v>
@@ -14045,7 +14049,7 @@
         <v>4823</v>
       </c>
       <c r="D368" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E368">
         <v>60</v>
@@ -14080,7 +14084,7 @@
         <v>4823</v>
       </c>
       <c r="D369" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E369">
         <v>100</v>
@@ -14115,7 +14119,7 @@
         <v>4823</v>
       </c>
       <c r="D370" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E370">
         <v>140</v>
@@ -14150,7 +14154,7 @@
         <v>4823</v>
       </c>
       <c r="D371" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E371">
         <v>180</v>
@@ -14185,7 +14189,7 @@
         <v>5207</v>
       </c>
       <c r="D372" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E372">
         <v>20</v>
@@ -14220,7 +14224,7 @@
         <v>5207</v>
       </c>
       <c r="D373" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E373">
         <v>60</v>
@@ -14255,7 +14259,7 @@
         <v>5207</v>
       </c>
       <c r="D374" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E374">
         <v>100</v>
@@ -14290,7 +14294,7 @@
         <v>5207</v>
       </c>
       <c r="D375" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E375">
         <v>140</v>
@@ -14325,7 +14329,7 @@
         <v>5207</v>
       </c>
       <c r="D376" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E376">
         <v>180</v>
@@ -14360,7 +14364,7 @@
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E377">
         <v>20</v>
@@ -14395,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E378">
         <v>60</v>
@@ -14430,7 +14434,7 @@
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E379">
         <v>100</v>
@@ -14465,7 +14469,7 @@
         <v>1</v>
       </c>
       <c r="D380" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E380">
         <v>140</v>
@@ -14500,7 +14504,7 @@
         <v>1</v>
       </c>
       <c r="D381" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E381">
         <v>180</v>
@@ -14535,7 +14539,7 @@
         <v>2</v>
       </c>
       <c r="D382" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E382">
         <v>20</v>
@@ -14570,7 +14574,7 @@
         <v>2</v>
       </c>
       <c r="D383" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E383">
         <v>60</v>
@@ -14605,7 +14609,7 @@
         <v>2</v>
       </c>
       <c r="D384" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E384">
         <v>100</v>
@@ -14640,7 +14644,7 @@
         <v>2</v>
       </c>
       <c r="D385" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E385">
         <v>140</v>
@@ -14675,7 +14679,7 @@
         <v>2</v>
       </c>
       <c r="D386" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E386">
         <v>180</v>
@@ -14710,7 +14714,7 @@
         <v>3</v>
       </c>
       <c r="D387" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E387">
         <v>20</v>
@@ -14745,7 +14749,7 @@
         <v>3</v>
       </c>
       <c r="D388" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E388">
         <v>60</v>
@@ -14780,7 +14784,7 @@
         <v>3</v>
       </c>
       <c r="D389" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E389">
         <v>100</v>
@@ -14815,7 +14819,7 @@
         <v>3</v>
       </c>
       <c r="D390" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E390">
         <v>140</v>
@@ -14850,7 +14854,7 @@
         <v>3</v>
       </c>
       <c r="D391" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E391">
         <v>180</v>
@@ -14882,10 +14886,10 @@
         <v>42795</v>
       </c>
       <c r="C392" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D392" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E392">
         <v>20</v>
@@ -14917,10 +14921,10 @@
         <v>42795</v>
       </c>
       <c r="C393" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D393" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E393">
         <v>60</v>
@@ -14952,10 +14956,10 @@
         <v>42795</v>
       </c>
       <c r="C394" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D394" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E394">
         <v>100</v>
@@ -14987,10 +14991,10 @@
         <v>42795</v>
       </c>
       <c r="C395" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D395" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E395">
         <v>140</v>
@@ -15022,10 +15026,10 @@
         <v>42795</v>
       </c>
       <c r="C396" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D396" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E396">
         <v>180</v>
@@ -15057,10 +15061,10 @@
         <v>42795</v>
       </c>
       <c r="C397" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E397">
         <v>20</v>
@@ -15092,10 +15096,10 @@
         <v>42795</v>
       </c>
       <c r="C398" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D398" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E398">
         <v>60</v>
@@ -15127,10 +15131,10 @@
         <v>42795</v>
       </c>
       <c r="C399" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D399" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E399">
         <v>100</v>
@@ -15162,10 +15166,10 @@
         <v>42795</v>
       </c>
       <c r="C400" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E400">
         <v>140</v>
@@ -15197,10 +15201,10 @@
         <v>42795</v>
       </c>
       <c r="C401" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D401" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E401">
         <v>180</v>
@@ -15232,10 +15236,10 @@
         <v>42795</v>
       </c>
       <c r="C402" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D402" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E402">
         <v>20</v>
@@ -15267,10 +15271,10 @@
         <v>42795</v>
       </c>
       <c r="C403" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D403" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E403">
         <v>60</v>
@@ -15302,10 +15306,10 @@
         <v>42795</v>
       </c>
       <c r="C404" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D404" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E404">
         <v>100</v>
@@ -15337,10 +15341,10 @@
         <v>42795</v>
       </c>
       <c r="C405" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D405" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E405">
         <v>140</v>
@@ -15372,10 +15376,10 @@
         <v>42795</v>
       </c>
       <c r="C406" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D406" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E406">
         <v>180</v>
@@ -15407,10 +15411,10 @@
         <v>42795</v>
       </c>
       <c r="C407" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D407" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E407">
         <v>20</v>
@@ -15442,10 +15446,10 @@
         <v>42795</v>
       </c>
       <c r="C408" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D408" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E408">
         <v>60</v>
@@ -15477,10 +15481,10 @@
         <v>42795</v>
       </c>
       <c r="C409" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D409" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E409">
         <v>100</v>
@@ -15512,10 +15516,10 @@
         <v>42795</v>
       </c>
       <c r="C410" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D410" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E410">
         <v>140</v>
@@ -15547,10 +15551,10 @@
         <v>42795</v>
       </c>
       <c r="C411" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D411" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E411">
         <v>180</v>
@@ -15582,10 +15586,10 @@
         <v>42795</v>
       </c>
       <c r="C412" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D412" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E412">
         <v>20</v>
@@ -15617,10 +15621,10 @@
         <v>42795</v>
       </c>
       <c r="C413" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D413" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E413">
         <v>60</v>
@@ -15652,10 +15656,10 @@
         <v>42795</v>
       </c>
       <c r="C414" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D414" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E414">
         <v>100</v>
@@ -15687,10 +15691,10 @@
         <v>42795</v>
       </c>
       <c r="C415" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D415" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E415">
         <v>140</v>
@@ -15722,10 +15726,10 @@
         <v>42795</v>
       </c>
       <c r="C416" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D416" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E416">
         <v>180</v>
@@ -15757,10 +15761,10 @@
         <v>42795</v>
       </c>
       <c r="C417" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D417" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E417">
         <v>20</v>
@@ -15792,10 +15796,10 @@
         <v>42795</v>
       </c>
       <c r="C418" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D418" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E418">
         <v>60</v>
@@ -15827,10 +15831,10 @@
         <v>42795</v>
       </c>
       <c r="C419" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D419" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E419">
         <v>100</v>
@@ -15862,10 +15866,10 @@
         <v>42795</v>
       </c>
       <c r="C420" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D420" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E420">
         <v>140</v>
@@ -15897,10 +15901,10 @@
         <v>42795</v>
       </c>
       <c r="C421" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D421" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E421">
         <v>180</v>
@@ -15932,10 +15936,10 @@
         <v>42795</v>
       </c>
       <c r="C422" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D422" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E422">
         <v>20</v>
@@ -15967,10 +15971,10 @@
         <v>42795</v>
       </c>
       <c r="C423" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D423" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E423">
         <v>60</v>
@@ -16002,10 +16006,10 @@
         <v>42795</v>
       </c>
       <c r="C424" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D424" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E424">
         <v>100</v>
@@ -16037,10 +16041,10 @@
         <v>42795</v>
       </c>
       <c r="C425" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D425" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E425">
         <v>140</v>
@@ -16072,10 +16076,10 @@
         <v>42795</v>
       </c>
       <c r="C426" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D426" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E426">
         <v>180</v>
@@ -16107,10 +16111,10 @@
         <v>42795</v>
       </c>
       <c r="C427" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D427" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E427">
         <v>20</v>
@@ -16142,10 +16146,10 @@
         <v>42795</v>
       </c>
       <c r="C428" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D428" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E428">
         <v>60</v>
@@ -16177,10 +16181,10 @@
         <v>42795</v>
       </c>
       <c r="C429" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D429" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E429">
         <v>100</v>
@@ -16212,10 +16216,10 @@
         <v>42795</v>
       </c>
       <c r="C430" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D430" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E430">
         <v>140</v>
@@ -16247,10 +16251,10 @@
         <v>42795</v>
       </c>
       <c r="C431" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D431" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E431">
         <v>180</v>
@@ -16282,10 +16286,10 @@
         <v>42795</v>
       </c>
       <c r="C432" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D432" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E432">
         <v>20</v>
@@ -16317,10 +16321,10 @@
         <v>42795</v>
       </c>
       <c r="C433" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D433" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E433">
         <v>60</v>
@@ -16352,10 +16356,10 @@
         <v>42795</v>
       </c>
       <c r="C434" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D434" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E434">
         <v>100</v>
@@ -16387,10 +16391,10 @@
         <v>42795</v>
       </c>
       <c r="C435" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D435" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E435">
         <v>140</v>
@@ -16422,10 +16426,10 @@
         <v>42795</v>
       </c>
       <c r="C436" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D436" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E436">
         <v>180</v>
@@ -16457,10 +16461,10 @@
         <v>42795</v>
       </c>
       <c r="C437" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D437" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E437">
         <v>20</v>
@@ -16492,10 +16496,10 @@
         <v>42795</v>
       </c>
       <c r="C438" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D438" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E438">
         <v>60</v>
@@ -16527,10 +16531,10 @@
         <v>42795</v>
       </c>
       <c r="C439" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D439" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E439">
         <v>100</v>
@@ -16562,10 +16566,10 @@
         <v>42795</v>
       </c>
       <c r="C440" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D440" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E440">
         <v>140</v>
@@ -16597,10 +16601,10 @@
         <v>42795</v>
       </c>
       <c r="C441" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D441" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E441">
         <v>180</v>
@@ -16632,10 +16636,10 @@
         <v>42795</v>
       </c>
       <c r="C442" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D442" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E442">
         <v>20</v>
@@ -16667,10 +16671,10 @@
         <v>42795</v>
       </c>
       <c r="C443" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D443" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E443">
         <v>60</v>
@@ -16702,10 +16706,10 @@
         <v>42795</v>
       </c>
       <c r="C444" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D444" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E444">
         <v>100</v>
@@ -16737,10 +16741,10 @@
         <v>42795</v>
       </c>
       <c r="C445" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D445" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E445">
         <v>140</v>
@@ -16772,10 +16776,10 @@
         <v>42795</v>
       </c>
       <c r="C446" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D446" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E446">
         <v>180</v>
@@ -16807,10 +16811,10 @@
         <v>42795</v>
       </c>
       <c r="C447" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D447" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E447">
         <v>20</v>
@@ -16842,10 +16846,10 @@
         <v>42795</v>
       </c>
       <c r="C448" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D448" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E448">
         <v>60</v>
@@ -16877,10 +16881,10 @@
         <v>42795</v>
       </c>
       <c r="C449" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D449" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E449">
         <v>100</v>
@@ -16912,10 +16916,10 @@
         <v>42795</v>
       </c>
       <c r="C450" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D450" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E450">
         <v>140</v>
@@ -16947,10 +16951,10 @@
         <v>42795</v>
       </c>
       <c r="C451" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D451" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E451">
         <v>180</v>
@@ -16982,10 +16986,10 @@
         <v>42795</v>
       </c>
       <c r="C452" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D452" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E452">
         <v>20</v>
@@ -17017,10 +17021,10 @@
         <v>42795</v>
       </c>
       <c r="C453" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D453" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E453">
         <v>60</v>
@@ -17052,10 +17056,10 @@
         <v>42795</v>
       </c>
       <c r="C454" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D454" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E454">
         <v>100</v>
@@ -17087,10 +17091,10 @@
         <v>42795</v>
       </c>
       <c r="C455" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D455" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E455">
         <v>140</v>
@@ -17122,10 +17126,10 @@
         <v>42795</v>
       </c>
       <c r="C456" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D456" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E456">
         <v>180</v>
@@ -17157,10 +17161,10 @@
         <v>42795</v>
       </c>
       <c r="C457" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D457" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E457">
         <v>20</v>
@@ -17192,10 +17196,10 @@
         <v>42795</v>
       </c>
       <c r="C458" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D458" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E458">
         <v>60</v>
@@ -17227,10 +17231,10 @@
         <v>42795</v>
       </c>
       <c r="C459" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D459" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E459">
         <v>100</v>
@@ -17262,10 +17266,10 @@
         <v>42795</v>
       </c>
       <c r="C460" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D460" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E460">
         <v>140</v>
@@ -17297,10 +17301,10 @@
         <v>42795</v>
       </c>
       <c r="C461" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D461" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E461">
         <v>180</v>
@@ -17332,10 +17336,10 @@
         <v>42795</v>
       </c>
       <c r="C462" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D462" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E462">
         <v>20</v>
@@ -17367,10 +17371,10 @@
         <v>42795</v>
       </c>
       <c r="C463" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D463" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E463">
         <v>60</v>
@@ -17402,10 +17406,10 @@
         <v>42795</v>
       </c>
       <c r="C464" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D464" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E464">
         <v>100</v>
@@ -17437,10 +17441,10 @@
         <v>42795</v>
       </c>
       <c r="C465" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D465" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E465">
         <v>140</v>
@@ -17472,10 +17476,10 @@
         <v>42795</v>
       </c>
       <c r="C466" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D466" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E466">
         <v>180</v>
@@ -17507,10 +17511,10 @@
         <v>42795</v>
       </c>
       <c r="C467" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D467" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E467">
         <v>20</v>
@@ -17542,10 +17546,10 @@
         <v>42795</v>
       </c>
       <c r="C468" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D468" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E468">
         <v>60</v>
@@ -17577,10 +17581,10 @@
         <v>42795</v>
       </c>
       <c r="C469" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D469" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E469">
         <v>100</v>
@@ -17612,10 +17616,10 @@
         <v>42795</v>
       </c>
       <c r="C470" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D470" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E470">
         <v>140</v>
@@ -17647,10 +17651,10 @@
         <v>42795</v>
       </c>
       <c r="C471" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D471" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E471">
         <v>180</v>
@@ -17682,10 +17686,10 @@
         <v>42795</v>
       </c>
       <c r="C472" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D472" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E472">
         <v>20</v>
@@ -17717,10 +17721,10 @@
         <v>42795</v>
       </c>
       <c r="C473" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D473" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E473">
         <v>60</v>
@@ -17752,10 +17756,10 @@
         <v>42795</v>
       </c>
       <c r="C474" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D474" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E474">
         <v>100</v>
@@ -17787,10 +17791,10 @@
         <v>42795</v>
       </c>
       <c r="C475" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D475" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E475">
         <v>140</v>
@@ -17822,10 +17826,10 @@
         <v>42795</v>
       </c>
       <c r="C476" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D476" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E476">
         <v>20</v>
@@ -17857,10 +17861,10 @@
         <v>42795</v>
       </c>
       <c r="C477" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D477" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E477">
         <v>60</v>
@@ -17892,10 +17896,10 @@
         <v>42795</v>
       </c>
       <c r="C478" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D478" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E478">
         <v>100</v>
@@ -17927,10 +17931,10 @@
         <v>42795</v>
       </c>
       <c r="C479" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D479" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E479">
         <v>140</v>
@@ -17962,10 +17966,10 @@
         <v>42795</v>
       </c>
       <c r="C480" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D480" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E480">
         <v>180</v>
@@ -17997,10 +18001,10 @@
         <v>42795</v>
       </c>
       <c r="C481" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D481" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E481">
         <v>20</v>
@@ -18032,10 +18036,10 @@
         <v>42795</v>
       </c>
       <c r="C482" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D482" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E482">
         <v>60</v>
@@ -18067,10 +18071,10 @@
         <v>42795</v>
       </c>
       <c r="C483" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D483" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E483">
         <v>100</v>
@@ -18102,10 +18106,10 @@
         <v>42795</v>
       </c>
       <c r="C484" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D484" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E484">
         <v>140</v>
@@ -18137,10 +18141,10 @@
         <v>42795</v>
       </c>
       <c r="C485" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D485" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E485">
         <v>180</v>
@@ -18172,10 +18176,10 @@
         <v>42795</v>
       </c>
       <c r="C486" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D486" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E486">
         <v>20</v>
@@ -18207,10 +18211,10 @@
         <v>42795</v>
       </c>
       <c r="C487" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D487" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E487">
         <v>60</v>
@@ -18242,10 +18246,10 @@
         <v>42795</v>
       </c>
       <c r="C488" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D488" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E488">
         <v>100</v>
@@ -18277,10 +18281,10 @@
         <v>42795</v>
       </c>
       <c r="C489" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D489" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E489">
         <v>140</v>
@@ -18312,10 +18316,10 @@
         <v>42795</v>
       </c>
       <c r="C490" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D490" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E490">
         <v>180</v>
@@ -18347,10 +18351,10 @@
         <v>42795</v>
       </c>
       <c r="C491" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D491" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E491">
         <v>20</v>
@@ -18382,10 +18386,10 @@
         <v>42795</v>
       </c>
       <c r="C492" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D492" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E492">
         <v>60</v>
@@ -18417,10 +18421,10 @@
         <v>42795</v>
       </c>
       <c r="C493" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D493" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E493">
         <v>100</v>
@@ -18452,10 +18456,10 @@
         <v>42795</v>
       </c>
       <c r="C494" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D494" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E494">
         <v>140</v>
@@ -18487,10 +18491,10 @@
         <v>42795</v>
       </c>
       <c r="C495" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D495" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E495">
         <v>20</v>
@@ -18522,10 +18526,10 @@
         <v>42795</v>
       </c>
       <c r="C496" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D496" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E496">
         <v>60</v>
@@ -18557,10 +18561,10 @@
         <v>42795</v>
       </c>
       <c r="C497" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D497" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E497">
         <v>100</v>
@@ -18592,10 +18596,10 @@
         <v>42795</v>
       </c>
       <c r="C498" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D498" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E498">
         <v>140</v>
@@ -18627,10 +18631,10 @@
         <v>42795</v>
       </c>
       <c r="C499" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D499" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E499">
         <v>180</v>
@@ -18662,10 +18666,10 @@
         <v>42795</v>
       </c>
       <c r="C500" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D500" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E500">
         <v>20</v>
@@ -18697,10 +18701,10 @@
         <v>42795</v>
       </c>
       <c r="C501" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D501" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E501">
         <v>60</v>
@@ -18732,10 +18736,10 @@
         <v>42795</v>
       </c>
       <c r="C502" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D502" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E502">
         <v>100</v>
@@ -18767,10 +18771,10 @@
         <v>42795</v>
       </c>
       <c r="C503" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D503" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E503">
         <v>140</v>
@@ -18802,10 +18806,10 @@
         <v>42795</v>
       </c>
       <c r="C504" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D504" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E504">
         <v>180</v>
@@ -18837,10 +18841,10 @@
         <v>42795</v>
       </c>
       <c r="C505" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D505" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E505">
         <v>20</v>
@@ -18872,10 +18876,10 @@
         <v>42795</v>
       </c>
       <c r="C506" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D506" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E506">
         <v>60</v>
@@ -18907,10 +18911,10 @@
         <v>42795</v>
       </c>
       <c r="C507" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D507" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E507">
         <v>100</v>
@@ -18942,10 +18946,10 @@
         <v>42795</v>
       </c>
       <c r="C508" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D508" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E508">
         <v>140</v>
@@ -18977,10 +18981,10 @@
         <v>42795</v>
       </c>
       <c r="C509" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D509" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E509">
         <v>180</v>
@@ -19012,10 +19016,10 @@
         <v>42795</v>
       </c>
       <c r="C510" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D510" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E510">
         <v>20</v>
@@ -19047,10 +19051,10 @@
         <v>42795</v>
       </c>
       <c r="C511" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D511" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E511">
         <v>60</v>
@@ -19082,10 +19086,10 @@
         <v>42795</v>
       </c>
       <c r="C512" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D512" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E512">
         <v>100</v>
@@ -19117,10 +19121,10 @@
         <v>42795</v>
       </c>
       <c r="C513" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D513" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E513">
         <v>140</v>
@@ -19152,10 +19156,10 @@
         <v>42795</v>
       </c>
       <c r="C514" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D514" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E514">
         <v>180</v>
@@ -19187,10 +19191,10 @@
         <v>42795</v>
       </c>
       <c r="C515" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D515" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E515">
         <v>20</v>
@@ -19222,10 +19226,10 @@
         <v>42795</v>
       </c>
       <c r="C516" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D516" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E516">
         <v>60</v>
@@ -19257,10 +19261,10 @@
         <v>42795</v>
       </c>
       <c r="C517" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D517" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E517">
         <v>100</v>
@@ -19292,10 +19296,10 @@
         <v>42795</v>
       </c>
       <c r="C518" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D518" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E518">
         <v>140</v>
@@ -19327,10 +19331,10 @@
         <v>42795</v>
       </c>
       <c r="C519" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D519" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E519">
         <v>180</v>
@@ -19362,10 +19366,10 @@
         <v>42795</v>
       </c>
       <c r="C520" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D520" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E520">
         <v>20</v>
@@ -19397,10 +19401,10 @@
         <v>42795</v>
       </c>
       <c r="C521" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D521" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E521">
         <v>60</v>
@@ -19432,10 +19436,10 @@
         <v>42795</v>
       </c>
       <c r="C522" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D522" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E522">
         <v>100</v>
@@ -19467,10 +19471,10 @@
         <v>42795</v>
       </c>
       <c r="C523" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D523" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E523">
         <v>140</v>
@@ -19502,10 +19506,10 @@
         <v>42795</v>
       </c>
       <c r="C524" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D524" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E524">
         <v>180</v>
@@ -19537,10 +19541,10 @@
         <v>42795</v>
       </c>
       <c r="C525" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D525" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E525">
         <v>20</v>
@@ -19572,10 +19576,10 @@
         <v>42795</v>
       </c>
       <c r="C526" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D526" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E526">
         <v>60</v>
@@ -19607,10 +19611,10 @@
         <v>42795</v>
       </c>
       <c r="C527" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D527" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E527">
         <v>100</v>
@@ -19642,10 +19646,10 @@
         <v>42795</v>
       </c>
       <c r="C528" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D528" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E528">
         <v>140</v>
@@ -19677,10 +19681,10 @@
         <v>42795</v>
       </c>
       <c r="C529" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D529" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E529">
         <v>180</v>
@@ -19712,10 +19716,10 @@
         <v>42795</v>
       </c>
       <c r="C530" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D530" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E530">
         <v>20</v>
@@ -19747,10 +19751,10 @@
         <v>42795</v>
       </c>
       <c r="C531" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D531" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E531">
         <v>60</v>
@@ -19782,10 +19786,10 @@
         <v>42795</v>
       </c>
       <c r="C532" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D532" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E532">
         <v>100</v>
@@ -19817,10 +19821,10 @@
         <v>42795</v>
       </c>
       <c r="C533" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D533" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E533">
         <v>140</v>
@@ -19852,10 +19856,10 @@
         <v>42795</v>
       </c>
       <c r="C534" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D534" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E534">
         <v>180</v>
@@ -19887,10 +19891,10 @@
         <v>42795</v>
       </c>
       <c r="C535" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D535" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E535">
         <v>20</v>
@@ -19922,10 +19926,10 @@
         <v>42795</v>
       </c>
       <c r="C536" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D536" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E536">
         <v>60</v>
@@ -19957,10 +19961,10 @@
         <v>42795</v>
       </c>
       <c r="C537" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D537" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E537">
         <v>100</v>
@@ -19992,10 +19996,10 @@
         <v>42795</v>
       </c>
       <c r="C538" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D538" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E538">
         <v>140</v>
@@ -20027,10 +20031,10 @@
         <v>42795</v>
       </c>
       <c r="C539" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D539" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E539">
         <v>180</v>
@@ -20062,10 +20066,10 @@
         <v>42795</v>
       </c>
       <c r="C540" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D540" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E540">
         <v>20</v>
@@ -20097,10 +20101,10 @@
         <v>42795</v>
       </c>
       <c r="C541" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D541" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E541">
         <v>60</v>
@@ -20132,10 +20136,10 @@
         <v>42795</v>
       </c>
       <c r="C542" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D542" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E542">
         <v>100</v>
@@ -20167,10 +20171,10 @@
         <v>42795</v>
       </c>
       <c r="C543" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D543" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E543">
         <v>140</v>
@@ -20202,10 +20206,10 @@
         <v>42795</v>
       </c>
       <c r="C544" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D544" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E544">
         <v>180</v>
@@ -20237,10 +20241,10 @@
         <v>42795</v>
       </c>
       <c r="C545" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D545" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E545">
         <v>20</v>
@@ -20272,10 +20276,10 @@
         <v>42795</v>
       </c>
       <c r="C546" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D546" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E546">
         <v>60</v>
@@ -20307,10 +20311,10 @@
         <v>42795</v>
       </c>
       <c r="C547" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D547" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E547">
         <v>100</v>
@@ -20342,10 +20346,10 @@
         <v>42795</v>
       </c>
       <c r="C548" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D548" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E548">
         <v>140</v>
@@ -20377,10 +20381,10 @@
         <v>42795</v>
       </c>
       <c r="C549" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D549" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E549">
         <v>180</v>
@@ -20412,10 +20416,10 @@
         <v>42795</v>
       </c>
       <c r="C550" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D550" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E550">
         <v>20</v>
@@ -20447,10 +20451,10 @@
         <v>42795</v>
       </c>
       <c r="C551" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D551" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E551">
         <v>60</v>
@@ -20482,10 +20486,10 @@
         <v>42795</v>
       </c>
       <c r="C552" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D552" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E552">
         <v>100</v>
@@ -20517,10 +20521,10 @@
         <v>42795</v>
       </c>
       <c r="C553" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D553" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E553">
         <v>140</v>
@@ -20552,10 +20556,10 @@
         <v>42795</v>
       </c>
       <c r="C554" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D554" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E554">
         <v>180</v>
@@ -20587,10 +20591,10 @@
         <v>42795</v>
       </c>
       <c r="C555" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D555" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E555">
         <v>20</v>
@@ -20622,10 +20626,10 @@
         <v>42795</v>
       </c>
       <c r="C556" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D556" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E556">
         <v>60</v>
@@ -20657,10 +20661,10 @@
         <v>42795</v>
       </c>
       <c r="C557" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D557" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E557">
         <v>100</v>
@@ -20692,10 +20696,10 @@
         <v>42795</v>
       </c>
       <c r="C558" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D558" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E558">
         <v>140</v>
@@ -20727,10 +20731,10 @@
         <v>42795</v>
       </c>
       <c r="C559" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D559" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E559">
         <v>180</v>
@@ -20762,10 +20766,10 @@
         <v>42810</v>
       </c>
       <c r="C560" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D560" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E560">
         <v>20</v>
@@ -20797,10 +20801,10 @@
         <v>42810</v>
       </c>
       <c r="C561" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D561" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E561">
         <v>60</v>
@@ -20832,10 +20836,10 @@
         <v>42810</v>
       </c>
       <c r="C562" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D562" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E562">
         <v>100</v>
@@ -20867,10 +20871,10 @@
         <v>42810</v>
       </c>
       <c r="C563" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D563" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E563">
         <v>140</v>
@@ -20902,10 +20906,10 @@
         <v>42810</v>
       </c>
       <c r="C564" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D564" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E564">
         <v>180</v>
@@ -20937,10 +20941,10 @@
         <v>42810</v>
       </c>
       <c r="C565" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D565" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E565">
         <v>20</v>
@@ -20972,10 +20976,10 @@
         <v>42810</v>
       </c>
       <c r="C566" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D566" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E566">
         <v>60</v>
@@ -21007,10 +21011,10 @@
         <v>42810</v>
       </c>
       <c r="C567" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D567" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E567">
         <v>100</v>
@@ -21042,10 +21046,10 @@
         <v>42810</v>
       </c>
       <c r="C568" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D568" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E568">
         <v>140</v>
@@ -21077,10 +21081,10 @@
         <v>42810</v>
       </c>
       <c r="C569" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D569" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E569">
         <v>180</v>
@@ -21112,10 +21116,10 @@
         <v>42810</v>
       </c>
       <c r="C570" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D570" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E570">
         <v>20</v>
@@ -21147,10 +21151,10 @@
         <v>42810</v>
       </c>
       <c r="C571" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D571" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E571">
         <v>60</v>
@@ -21182,10 +21186,10 @@
         <v>42810</v>
       </c>
       <c r="C572" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D572" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E572">
         <v>100</v>
@@ -21217,10 +21221,10 @@
         <v>42810</v>
       </c>
       <c r="C573" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D573" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E573">
         <v>140</v>
@@ -21252,10 +21256,10 @@
         <v>42810</v>
       </c>
       <c r="C574" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D574" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E574">
         <v>180</v>
@@ -21287,10 +21291,10 @@
         <v>42810</v>
       </c>
       <c r="C575" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D575" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E575">
         <v>20</v>
@@ -21322,10 +21326,10 @@
         <v>42810</v>
       </c>
       <c r="C576" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D576" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E576">
         <v>60</v>
@@ -21357,10 +21361,10 @@
         <v>42810</v>
       </c>
       <c r="C577" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D577" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E577">
         <v>100</v>
@@ -21392,10 +21396,10 @@
         <v>42810</v>
       </c>
       <c r="C578" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D578" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E578">
         <v>140</v>
@@ -21427,10 +21431,10 @@
         <v>42810</v>
       </c>
       <c r="C579" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D579" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E579">
         <v>180</v>
@@ -21462,10 +21466,10 @@
         <v>42810</v>
       </c>
       <c r="C580" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D580" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E580">
         <v>20</v>
@@ -21497,10 +21501,10 @@
         <v>42810</v>
       </c>
       <c r="C581" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D581" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E581">
         <v>60</v>
@@ -21532,10 +21536,10 @@
         <v>42810</v>
       </c>
       <c r="C582" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D582" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E582">
         <v>100</v>
@@ -21567,10 +21571,10 @@
         <v>42810</v>
       </c>
       <c r="C583" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D583" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E583">
         <v>140</v>
@@ -21602,10 +21606,10 @@
         <v>42810</v>
       </c>
       <c r="C584" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D584" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E584">
         <v>180</v>
@@ -21637,10 +21641,10 @@
         <v>42810</v>
       </c>
       <c r="C585" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D585" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E585">
         <v>20</v>
@@ -21672,10 +21676,10 @@
         <v>42810</v>
       </c>
       <c r="C586" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D586" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E586">
         <v>60</v>
@@ -21707,10 +21711,10 @@
         <v>42810</v>
       </c>
       <c r="C587" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D587" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E587">
         <v>100</v>
@@ -21742,10 +21746,10 @@
         <v>42810</v>
       </c>
       <c r="C588" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D588" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E588">
         <v>140</v>
@@ -21777,10 +21781,10 @@
         <v>42810</v>
       </c>
       <c r="C589" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D589" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E589">
         <v>180</v>
@@ -21812,10 +21816,10 @@
         <v>42810</v>
       </c>
       <c r="C590" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D590" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E590">
         <v>20</v>
@@ -21847,10 +21851,10 @@
         <v>42810</v>
       </c>
       <c r="C591" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D591" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E591">
         <v>60</v>
@@ -21882,10 +21886,10 @@
         <v>42810</v>
       </c>
       <c r="C592" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D592" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E592">
         <v>100</v>
@@ -21917,10 +21921,10 @@
         <v>42810</v>
       </c>
       <c r="C593" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D593" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E593">
         <v>140</v>
@@ -21952,10 +21956,10 @@
         <v>42810</v>
       </c>
       <c r="C594" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D594" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E594">
         <v>180</v>
@@ -21987,10 +21991,10 @@
         <v>42810</v>
       </c>
       <c r="C595" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D595" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E595">
         <v>20</v>
@@ -22022,10 +22026,10 @@
         <v>42810</v>
       </c>
       <c r="C596" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D596" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E596">
         <v>60</v>
@@ -22057,10 +22061,10 @@
         <v>42810</v>
       </c>
       <c r="C597" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D597" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E597">
         <v>100</v>
@@ -22092,10 +22096,10 @@
         <v>42810</v>
       </c>
       <c r="C598" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D598" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E598">
         <v>140</v>
@@ -22127,10 +22131,10 @@
         <v>42810</v>
       </c>
       <c r="C599" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D599" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E599">
         <v>180</v>
@@ -22162,10 +22166,10 @@
         <v>42810</v>
       </c>
       <c r="C600" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D600" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E600">
         <v>20</v>
@@ -22197,10 +22201,10 @@
         <v>42810</v>
       </c>
       <c r="C601" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D601" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E601">
         <v>60</v>
@@ -22232,10 +22236,10 @@
         <v>42810</v>
       </c>
       <c r="C602" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D602" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E602">
         <v>100</v>
@@ -22267,10 +22271,10 @@
         <v>42810</v>
       </c>
       <c r="C603" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D603" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E603">
         <v>140</v>
@@ -22302,10 +22306,10 @@
         <v>42810</v>
       </c>
       <c r="C604" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D604" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E604">
         <v>180</v>
@@ -22337,10 +22341,10 @@
         <v>42810</v>
       </c>
       <c r="C605" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D605" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E605">
         <v>20</v>
@@ -22372,10 +22376,10 @@
         <v>42810</v>
       </c>
       <c r="C606" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D606" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E606">
         <v>60</v>
@@ -22407,10 +22411,10 @@
         <v>42810</v>
       </c>
       <c r="C607" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D607" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E607">
         <v>100</v>
@@ -22442,10 +22446,10 @@
         <v>42810</v>
       </c>
       <c r="C608" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D608" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E608">
         <v>140</v>
@@ -22477,10 +22481,10 @@
         <v>42810</v>
       </c>
       <c r="C609" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D609" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E609">
         <v>180</v>
@@ -22512,10 +22516,10 @@
         <v>42810</v>
       </c>
       <c r="C610" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D610" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E610">
         <v>20</v>
@@ -22547,10 +22551,10 @@
         <v>42810</v>
       </c>
       <c r="C611" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D611" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E611">
         <v>60</v>
@@ -22582,10 +22586,10 @@
         <v>42810</v>
       </c>
       <c r="C612" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D612" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E612">
         <v>100</v>
@@ -22617,10 +22621,10 @@
         <v>42810</v>
       </c>
       <c r="C613" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D613" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E613">
         <v>140</v>
@@ -22652,10 +22656,10 @@
         <v>42810</v>
       </c>
       <c r="C614" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D614" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E614">
         <v>180</v>
@@ -22687,10 +22691,10 @@
         <v>42810</v>
       </c>
       <c r="C615" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D615" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E615">
         <v>20</v>
@@ -22722,10 +22726,10 @@
         <v>42810</v>
       </c>
       <c r="C616" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D616" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E616">
         <v>60</v>
@@ -22757,10 +22761,10 @@
         <v>42810</v>
       </c>
       <c r="C617" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D617" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E617">
         <v>100</v>
@@ -22792,10 +22796,10 @@
         <v>42810</v>
       </c>
       <c r="C618" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D618" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E618">
         <v>140</v>
@@ -22827,10 +22831,10 @@
         <v>42810</v>
       </c>
       <c r="C619" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D619" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E619">
         <v>180</v>
@@ -22862,10 +22866,10 @@
         <v>42810</v>
       </c>
       <c r="C620" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D620" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E620">
         <v>20</v>
@@ -22897,10 +22901,10 @@
         <v>42810</v>
       </c>
       <c r="C621" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D621" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E621">
         <v>60</v>
@@ -22932,10 +22936,10 @@
         <v>42810</v>
       </c>
       <c r="C622" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D622" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E622">
         <v>100</v>
@@ -22967,10 +22971,10 @@
         <v>42810</v>
       </c>
       <c r="C623" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D623" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E623">
         <v>20</v>
@@ -23002,10 +23006,10 @@
         <v>42810</v>
       </c>
       <c r="C624" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D624" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E624">
         <v>60</v>
@@ -23037,10 +23041,10 @@
         <v>42810</v>
       </c>
       <c r="C625" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D625" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E625">
         <v>100</v>
@@ -23072,10 +23076,10 @@
         <v>42810</v>
       </c>
       <c r="C626" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D626" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E626">
         <v>140</v>
@@ -23107,10 +23111,10 @@
         <v>42810</v>
       </c>
       <c r="C627" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D627" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E627">
         <v>180</v>
@@ -23142,10 +23146,10 @@
         <v>42810</v>
       </c>
       <c r="C628" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D628" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E628">
         <v>20</v>
@@ -23177,10 +23181,10 @@
         <v>42810</v>
       </c>
       <c r="C629" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D629" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E629">
         <v>60</v>
@@ -23212,10 +23216,10 @@
         <v>42810</v>
       </c>
       <c r="C630" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D630" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E630">
         <v>100</v>
@@ -23247,10 +23251,10 @@
         <v>42810</v>
       </c>
       <c r="C631" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D631" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E631">
         <v>140</v>
@@ -23282,10 +23286,10 @@
         <v>42810</v>
       </c>
       <c r="C632" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D632" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E632">
         <v>180</v>
@@ -23317,10 +23321,10 @@
         <v>42810</v>
       </c>
       <c r="C633" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D633" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E633">
         <v>20</v>
@@ -23352,10 +23356,10 @@
         <v>42810</v>
       </c>
       <c r="C634" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D634" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E634">
         <v>60</v>
@@ -23387,10 +23391,10 @@
         <v>42810</v>
       </c>
       <c r="C635" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D635" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E635">
         <v>100</v>
@@ -23422,10 +23426,10 @@
         <v>42810</v>
       </c>
       <c r="C636" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D636" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E636">
         <v>140</v>
@@ -23457,10 +23461,10 @@
         <v>42810</v>
       </c>
       <c r="C637" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D637" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E637">
         <v>180</v>
@@ -23492,10 +23496,10 @@
         <v>42810</v>
       </c>
       <c r="C638" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D638" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E638">
         <v>20</v>
@@ -23527,10 +23531,10 @@
         <v>42810</v>
       </c>
       <c r="C639" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D639" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E639">
         <v>60</v>
@@ -23562,10 +23566,10 @@
         <v>42810</v>
       </c>
       <c r="C640" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D640" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E640">
         <v>100</v>
@@ -23597,10 +23601,10 @@
         <v>42810</v>
       </c>
       <c r="C641" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D641" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E641">
         <v>140</v>
@@ -23632,10 +23636,10 @@
         <v>42810</v>
       </c>
       <c r="C642" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D642" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E642">
         <v>180</v>
@@ -23667,10 +23671,10 @@
         <v>42810</v>
       </c>
       <c r="C643" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D643" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E643">
         <v>20</v>
@@ -23702,10 +23706,10 @@
         <v>42810</v>
       </c>
       <c r="C644" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D644" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E644">
         <v>60</v>
@@ -23737,10 +23741,10 @@
         <v>42810</v>
       </c>
       <c r="C645" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D645" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E645">
         <v>100</v>
@@ -23772,10 +23776,10 @@
         <v>42810</v>
       </c>
       <c r="C646" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D646" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E646">
         <v>140</v>
@@ -23807,10 +23811,10 @@
         <v>42810</v>
       </c>
       <c r="C647" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D647" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E647">
         <v>180</v>
@@ -23842,10 +23846,10 @@
         <v>42810</v>
       </c>
       <c r="C648" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D648" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E648">
         <v>20</v>
@@ -23877,10 +23881,10 @@
         <v>42810</v>
       </c>
       <c r="C649" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D649" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E649">
         <v>60</v>
@@ -23912,10 +23916,10 @@
         <v>42810</v>
       </c>
       <c r="C650" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D650" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E650">
         <v>100</v>
@@ -23947,10 +23951,10 @@
         <v>42810</v>
       </c>
       <c r="C651" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D651" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E651">
         <v>140</v>
@@ -23982,10 +23986,10 @@
         <v>42810</v>
       </c>
       <c r="C652" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D652" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E652">
         <v>180</v>
@@ -24017,10 +24021,10 @@
         <v>42810</v>
       </c>
       <c r="C653" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D653" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E653">
         <v>20</v>
@@ -24052,10 +24056,10 @@
         <v>42810</v>
       </c>
       <c r="C654" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D654" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E654">
         <v>60</v>
@@ -24087,10 +24091,10 @@
         <v>42810</v>
       </c>
       <c r="C655" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D655" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E655">
         <v>100</v>
@@ -24122,10 +24126,10 @@
         <v>42810</v>
       </c>
       <c r="C656" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D656" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E656">
         <v>140</v>
@@ -24157,10 +24161,10 @@
         <v>42810</v>
       </c>
       <c r="C657" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D657" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E657">
         <v>180</v>
@@ -24192,10 +24196,10 @@
         <v>42810</v>
       </c>
       <c r="C658" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D658" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E658">
         <v>20</v>
@@ -24227,10 +24231,10 @@
         <v>42810</v>
       </c>
       <c r="C659" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D659" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E659">
         <v>60</v>
@@ -24262,10 +24266,10 @@
         <v>42810</v>
       </c>
       <c r="C660" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D660" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E660">
         <v>100</v>
@@ -24297,10 +24301,10 @@
         <v>42810</v>
       </c>
       <c r="C661" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D661" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E661">
         <v>140</v>
@@ -24332,10 +24336,10 @@
         <v>42810</v>
       </c>
       <c r="C662" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D662" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E662">
         <v>180</v>
@@ -24367,10 +24371,10 @@
         <v>42810</v>
       </c>
       <c r="C663" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D663" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E663">
         <v>20</v>
@@ -24402,10 +24406,10 @@
         <v>42810</v>
       </c>
       <c r="C664" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D664" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E664">
         <v>60</v>
@@ -24437,10 +24441,10 @@
         <v>42810</v>
       </c>
       <c r="C665" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D665" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E665">
         <v>100</v>
@@ -24472,10 +24476,10 @@
         <v>42810</v>
       </c>
       <c r="C666" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D666" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E666">
         <v>140</v>
@@ -24507,10 +24511,10 @@
         <v>42810</v>
       </c>
       <c r="C667" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D667" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E667">
         <v>180</v>
@@ -24542,10 +24546,10 @@
         <v>42810</v>
       </c>
       <c r="C668" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D668" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E668">
         <v>20</v>
@@ -24577,10 +24581,10 @@
         <v>42810</v>
       </c>
       <c r="C669" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D669" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E669">
         <v>60</v>
@@ -24612,10 +24616,10 @@
         <v>42810</v>
       </c>
       <c r="C670" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D670" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E670">
         <v>100</v>
@@ -24647,10 +24651,10 @@
         <v>42810</v>
       </c>
       <c r="C671" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D671" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E671">
         <v>20</v>
@@ -24682,10 +24686,10 @@
         <v>42810</v>
       </c>
       <c r="C672" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D672" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E672">
         <v>60</v>
@@ -24717,10 +24721,10 @@
         <v>42810</v>
       </c>
       <c r="C673" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D673" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E673">
         <v>100</v>
@@ -24752,10 +24756,10 @@
         <v>42810</v>
       </c>
       <c r="C674" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D674" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E674">
         <v>140</v>
@@ -24787,10 +24791,10 @@
         <v>42810</v>
       </c>
       <c r="C675" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D675" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E675">
         <v>20</v>
@@ -24822,10 +24826,10 @@
         <v>42810</v>
       </c>
       <c r="C676" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D676" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E676">
         <v>60</v>
@@ -24857,10 +24861,10 @@
         <v>42810</v>
       </c>
       <c r="C677" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D677" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E677">
         <v>100</v>
@@ -24892,10 +24896,10 @@
         <v>42810</v>
       </c>
       <c r="C678" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D678" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E678">
         <v>140</v>
@@ -24927,10 +24931,10 @@
         <v>42810</v>
       </c>
       <c r="C679" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D679" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E679">
         <v>180</v>
@@ -24962,10 +24966,10 @@
         <v>42810</v>
       </c>
       <c r="C680" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D680" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E680">
         <v>20</v>
@@ -24997,10 +25001,10 @@
         <v>42810</v>
       </c>
       <c r="C681" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D681" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E681">
         <v>60</v>
@@ -25032,10 +25036,10 @@
         <v>42810</v>
       </c>
       <c r="C682" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D682" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E682">
         <v>100</v>
@@ -25067,10 +25071,10 @@
         <v>42810</v>
       </c>
       <c r="C683" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D683" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E683">
         <v>140</v>
@@ -25102,10 +25106,10 @@
         <v>42810</v>
       </c>
       <c r="C684" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D684" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E684">
         <v>180</v>
@@ -25137,10 +25141,10 @@
         <v>42810</v>
       </c>
       <c r="C685" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D685" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E685">
         <v>20</v>
@@ -25172,10 +25176,10 @@
         <v>42810</v>
       </c>
       <c r="C686" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D686" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E686">
         <v>60</v>
@@ -25207,10 +25211,10 @@
         <v>42810</v>
       </c>
       <c r="C687" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D687" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E687">
         <v>100</v>
@@ -25242,10 +25246,10 @@
         <v>42810</v>
       </c>
       <c r="C688" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D688" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E688">
         <v>140</v>
@@ -25277,10 +25281,10 @@
         <v>42810</v>
       </c>
       <c r="C689" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D689" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E689">
         <v>180</v>
@@ -25312,10 +25316,10 @@
         <v>42810</v>
       </c>
       <c r="C690" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D690" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E690">
         <v>20</v>
@@ -25347,10 +25351,10 @@
         <v>42810</v>
       </c>
       <c r="C691" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D691" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E691">
         <v>60</v>
@@ -25382,10 +25386,10 @@
         <v>42810</v>
       </c>
       <c r="C692" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D692" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E692">
         <v>100</v>
@@ -25417,10 +25421,10 @@
         <v>42810</v>
       </c>
       <c r="C693" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D693" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E693">
         <v>140</v>
@@ -25452,10 +25456,10 @@
         <v>42810</v>
       </c>
       <c r="C694" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D694" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E694">
         <v>20</v>
@@ -25487,10 +25491,10 @@
         <v>42810</v>
       </c>
       <c r="C695" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D695" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E695">
         <v>60</v>
@@ -25522,10 +25526,10 @@
         <v>42810</v>
       </c>
       <c r="C696" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D696" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E696">
         <v>100</v>
@@ -25557,10 +25561,10 @@
         <v>42810</v>
       </c>
       <c r="C697" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D697" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E697">
         <v>140</v>
@@ -25592,10 +25596,10 @@
         <v>42810</v>
       </c>
       <c r="C698" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D698" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E698">
         <v>180</v>
@@ -25627,10 +25631,10 @@
         <v>42810</v>
       </c>
       <c r="C699" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D699" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E699">
         <v>20</v>
@@ -25662,10 +25666,10 @@
         <v>42810</v>
       </c>
       <c r="C700" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D700" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E700">
         <v>60</v>
@@ -25697,10 +25701,10 @@
         <v>42810</v>
       </c>
       <c r="C701" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D701" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E701">
         <v>100</v>
@@ -25732,10 +25736,10 @@
         <v>42810</v>
       </c>
       <c r="C702" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D702" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E702">
         <v>140</v>
@@ -25767,10 +25771,10 @@
         <v>42810</v>
       </c>
       <c r="C703" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D703" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E703">
         <v>180</v>
@@ -25802,10 +25806,10 @@
         <v>42810</v>
       </c>
       <c r="C704" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D704" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E704">
         <v>20</v>
@@ -25837,10 +25841,10 @@
         <v>42810</v>
       </c>
       <c r="C705" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D705" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E705">
         <v>60</v>
@@ -25872,10 +25876,10 @@
         <v>42810</v>
       </c>
       <c r="C706" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D706" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E706">
         <v>100</v>
@@ -25907,10 +25911,10 @@
         <v>42810</v>
       </c>
       <c r="C707" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D707" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E707">
         <v>140</v>
@@ -25942,10 +25946,10 @@
         <v>42810</v>
       </c>
       <c r="C708" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D708" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E708">
         <v>180</v>
@@ -25977,10 +25981,10 @@
         <v>42810</v>
       </c>
       <c r="C709" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D709" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E709">
         <v>20</v>
@@ -26012,10 +26016,10 @@
         <v>42810</v>
       </c>
       <c r="C710" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D710" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E710">
         <v>60</v>
@@ -26047,10 +26051,10 @@
         <v>42810</v>
       </c>
       <c r="C711" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D711" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E711">
         <v>100</v>
@@ -26082,10 +26086,10 @@
         <v>42810</v>
       </c>
       <c r="C712" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D712" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E712">
         <v>140</v>
@@ -26117,10 +26121,10 @@
         <v>42810</v>
       </c>
       <c r="C713" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D713" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E713">
         <v>180</v>
@@ -26152,10 +26156,10 @@
         <v>42810</v>
       </c>
       <c r="C714" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D714" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E714">
         <v>20</v>
@@ -26187,10 +26191,10 @@
         <v>42810</v>
       </c>
       <c r="C715" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D715" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E715">
         <v>60</v>
@@ -26222,10 +26226,10 @@
         <v>42810</v>
       </c>
       <c r="C716" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D716" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E716">
         <v>100</v>
@@ -26257,10 +26261,10 @@
         <v>42810</v>
       </c>
       <c r="C717" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D717" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E717">
         <v>140</v>
@@ -26292,10 +26296,10 @@
         <v>42810</v>
       </c>
       <c r="C718" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D718" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E718">
         <v>180</v>
@@ -26327,10 +26331,10 @@
         <v>42810</v>
       </c>
       <c r="C719" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D719" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E719">
         <v>20</v>
@@ -26362,10 +26366,10 @@
         <v>42810</v>
       </c>
       <c r="C720" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D720" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E720">
         <v>60</v>
@@ -26397,10 +26401,10 @@
         <v>42810</v>
       </c>
       <c r="C721" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D721" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E721">
         <v>100</v>
@@ -26432,10 +26436,10 @@
         <v>42810</v>
       </c>
       <c r="C722" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D722" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E722">
         <v>140</v>
@@ -26467,10 +26471,10 @@
         <v>42810</v>
       </c>
       <c r="C723" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D723" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E723">
         <v>180</v>
@@ -26502,10 +26506,10 @@
         <v>42810</v>
       </c>
       <c r="C724" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D724" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E724">
         <v>20</v>
@@ -26537,10 +26541,10 @@
         <v>42810</v>
       </c>
       <c r="C725" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D725" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E725">
         <v>60</v>
@@ -26572,10 +26576,10 @@
         <v>42810</v>
       </c>
       <c r="C726" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D726" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E726">
         <v>100</v>
@@ -26607,10 +26611,10 @@
         <v>42810</v>
       </c>
       <c r="C727" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D727" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E727">
         <v>140</v>
@@ -26642,10 +26646,10 @@
         <v>42810</v>
       </c>
       <c r="C728" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D728" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E728">
         <v>180</v>
@@ -26677,10 +26681,10 @@
         <v>42810</v>
       </c>
       <c r="C729" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D729" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E729">
         <v>20</v>
@@ -26712,10 +26716,10 @@
         <v>42810</v>
       </c>
       <c r="C730" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D730" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E730">
         <v>60</v>
@@ -26747,10 +26751,10 @@
         <v>42810</v>
       </c>
       <c r="C731" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D731" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E731">
         <v>100</v>
@@ -26782,10 +26786,10 @@
         <v>42810</v>
       </c>
       <c r="C732" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D732" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E732">
         <v>140</v>
@@ -26817,10 +26821,10 @@
         <v>42810</v>
       </c>
       <c r="C733" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D733" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E733">
         <v>180</v>
@@ -26852,10 +26856,10 @@
         <v>42810</v>
       </c>
       <c r="C734" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D734" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E734">
         <v>20</v>
@@ -26887,10 +26891,10 @@
         <v>42810</v>
       </c>
       <c r="C735" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D735" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E735">
         <v>60</v>
@@ -26922,10 +26926,10 @@
         <v>42810</v>
       </c>
       <c r="C736" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D736" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E736">
         <v>100</v>
@@ -26957,10 +26961,10 @@
         <v>42810</v>
       </c>
       <c r="C737" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D737" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E737">
         <v>140</v>
@@ -26992,10 +26996,10 @@
         <v>42810</v>
       </c>
       <c r="C738" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D738" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E738">
         <v>180</v>
@@ -27027,10 +27031,10 @@
         <v>42810</v>
       </c>
       <c r="C739" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D739" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E739">
         <v>20</v>
@@ -27062,10 +27066,10 @@
         <v>42810</v>
       </c>
       <c r="C740" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D740" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E740">
         <v>60</v>
@@ -27097,10 +27101,10 @@
         <v>42810</v>
       </c>
       <c r="C741" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D741" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E741">
         <v>100</v>
@@ -27132,10 +27136,10 @@
         <v>42810</v>
       </c>
       <c r="C742" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D742" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E742">
         <v>140</v>
@@ -27167,10 +27171,10 @@
         <v>42810</v>
       </c>
       <c r="C743" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D743" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E743">
         <v>180</v>
@@ -27202,10 +27206,10 @@
         <v>42810</v>
       </c>
       <c r="C744" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D744" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E744">
         <v>20</v>
@@ -27237,10 +27241,10 @@
         <v>42810</v>
       </c>
       <c r="C745" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D745" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E745">
         <v>60</v>
@@ -27272,10 +27276,10 @@
         <v>42810</v>
       </c>
       <c r="C746" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D746" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E746">
         <v>100</v>
@@ -27307,10 +27311,10 @@
         <v>42810</v>
       </c>
       <c r="C747" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D747" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E747">
         <v>140</v>
@@ -27342,10 +27346,10 @@
         <v>42810</v>
       </c>
       <c r="C748" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D748" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E748">
         <v>180</v>
@@ -27377,10 +27381,10 @@
         <v>42810</v>
       </c>
       <c r="C749" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D749" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E749">
         <v>20</v>
@@ -27412,10 +27416,10 @@
         <v>42810</v>
       </c>
       <c r="C750" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D750" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E750">
         <v>60</v>
@@ -27447,10 +27451,10 @@
         <v>42810</v>
       </c>
       <c r="C751" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D751" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E751">
         <v>100</v>
@@ -27482,10 +27486,10 @@
         <v>42810</v>
       </c>
       <c r="C752" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D752" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E752">
         <v>140</v>
@@ -27517,10 +27521,10 @@
         <v>42810</v>
       </c>
       <c r="C753" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D753" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E753">
         <v>180</v>
@@ -27552,10 +27556,10 @@
         <v>42856</v>
       </c>
       <c r="C754" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D754" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E754">
         <v>20</v>
@@ -27587,10 +27591,10 @@
         <v>42856</v>
       </c>
       <c r="C755" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D755" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E755">
         <v>60</v>
@@ -27622,10 +27626,10 @@
         <v>42856</v>
       </c>
       <c r="C756" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D756" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E756">
         <v>100</v>
@@ -27657,10 +27661,10 @@
         <v>42856</v>
       </c>
       <c r="C757" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D757" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E757">
         <v>140</v>
@@ -27692,10 +27696,10 @@
         <v>42856</v>
       </c>
       <c r="C758" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D758" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E758">
         <v>180</v>
@@ -27727,10 +27731,10 @@
         <v>42856</v>
       </c>
       <c r="C759" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D759" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E759">
         <v>20</v>
@@ -27762,10 +27766,10 @@
         <v>42856</v>
       </c>
       <c r="C760" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D760" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E760">
         <v>60</v>
@@ -27797,10 +27801,10 @@
         <v>42856</v>
       </c>
       <c r="C761" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D761" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E761">
         <v>100</v>
@@ -27832,10 +27836,10 @@
         <v>42856</v>
       </c>
       <c r="C762" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D762" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E762">
         <v>140</v>
@@ -27867,10 +27871,10 @@
         <v>42856</v>
       </c>
       <c r="C763" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D763" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E763">
         <v>180</v>
@@ -27902,10 +27906,10 @@
         <v>42856</v>
       </c>
       <c r="C764" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D764" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E764">
         <v>20</v>
@@ -27937,10 +27941,10 @@
         <v>42856</v>
       </c>
       <c r="C765" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D765" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E765">
         <v>60</v>
@@ -27972,10 +27976,10 @@
         <v>42856</v>
       </c>
       <c r="C766" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D766" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E766">
         <v>100</v>
@@ -28007,10 +28011,10 @@
         <v>42856</v>
       </c>
       <c r="C767" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D767" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E767">
         <v>140</v>
@@ -28042,10 +28046,10 @@
         <v>42856</v>
       </c>
       <c r="C768" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D768" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E768">
         <v>180</v>
@@ -28077,10 +28081,10 @@
         <v>42856</v>
       </c>
       <c r="C769" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D769" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E769">
         <v>20</v>
@@ -28112,10 +28116,10 @@
         <v>42856</v>
       </c>
       <c r="C770" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D770" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E770">
         <v>60</v>
@@ -28147,10 +28151,10 @@
         <v>42856</v>
       </c>
       <c r="C771" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D771" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E771">
         <v>100</v>
@@ -28182,10 +28186,10 @@
         <v>42856</v>
       </c>
       <c r="C772" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D772" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E772">
         <v>140</v>
@@ -28217,10 +28221,10 @@
         <v>42856</v>
       </c>
       <c r="C773" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D773" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E773">
         <v>180</v>
@@ -28252,10 +28256,10 @@
         <v>42856</v>
       </c>
       <c r="C774" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D774" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E774">
         <v>20</v>
@@ -28287,10 +28291,10 @@
         <v>42856</v>
       </c>
       <c r="C775" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D775" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E775">
         <v>60</v>
@@ -28322,10 +28326,10 @@
         <v>42856</v>
       </c>
       <c r="C776" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D776" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E776">
         <v>100</v>
@@ -28357,10 +28361,10 @@
         <v>42856</v>
       </c>
       <c r="C777" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D777" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E777">
         <v>140</v>
@@ -28392,10 +28396,10 @@
         <v>42856</v>
       </c>
       <c r="C778" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D778" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E778">
         <v>180</v>
@@ -28427,10 +28431,10 @@
         <v>42856</v>
       </c>
       <c r="C779" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D779" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E779">
         <v>20</v>
@@ -28462,10 +28466,10 @@
         <v>42856</v>
       </c>
       <c r="C780" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D780" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E780">
         <v>60</v>
@@ -28497,10 +28501,10 @@
         <v>42856</v>
       </c>
       <c r="C781" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D781" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E781">
         <v>100</v>
@@ -28532,10 +28536,10 @@
         <v>42856</v>
       </c>
       <c r="C782" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D782" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E782">
         <v>140</v>
@@ -28567,10 +28571,10 @@
         <v>42856</v>
       </c>
       <c r="C783" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D783" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E783">
         <v>180</v>
@@ -28602,10 +28606,10 @@
         <v>42856</v>
       </c>
       <c r="C784" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D784" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E784">
         <v>20</v>
@@ -28637,10 +28641,10 @@
         <v>42856</v>
       </c>
       <c r="C785" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D785" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E785">
         <v>60</v>
@@ -28672,10 +28676,10 @@
         <v>42856</v>
       </c>
       <c r="C786" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D786" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E786">
         <v>100</v>
@@ -28707,10 +28711,10 @@
         <v>42856</v>
       </c>
       <c r="C787" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D787" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E787">
         <v>140</v>
@@ -28742,10 +28746,10 @@
         <v>42856</v>
       </c>
       <c r="C788" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D788" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E788">
         <v>180</v>
@@ -28777,10 +28781,10 @@
         <v>42856</v>
       </c>
       <c r="C789" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D789" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E789">
         <v>20</v>
@@ -28812,10 +28816,10 @@
         <v>42856</v>
       </c>
       <c r="C790" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D790" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E790">
         <v>60</v>
@@ -28847,10 +28851,10 @@
         <v>42856</v>
       </c>
       <c r="C791" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D791" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E791">
         <v>100</v>
@@ -28882,10 +28886,10 @@
         <v>42856</v>
       </c>
       <c r="C792" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D792" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E792">
         <v>140</v>
@@ -28917,10 +28921,10 @@
         <v>42856</v>
       </c>
       <c r="C793" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D793" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E793">
         <v>180</v>
